--- a/VPD PO download generator/trying stuff business systems.xlsx
+++ b/VPD PO download generator/trying stuff business systems.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwa25\source\repos\VPD PO download generator\VPD PO download generator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C264A02F-5A34-4A22-9099-0A21EADD2A56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6AFC98A-44CD-481B-8099-64F0EE14F9C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{D51960FC-1269-4ACE-8C84-C0CBF6215B21}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{D51960FC-1269-4ACE-8C84-C0CBF6215B21}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="1st attempt optimization" sheetId="2" r:id="rId2"/>
     <sheet name="1st attempt optimization, part2" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="4" r:id="rId4"/>
+    <sheet name="orderLists" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1242" uniqueCount="133">
   <si>
     <t>KSO5088990 PVPDFJB    TWHWHNA01AA001CR-SO-5088990-1-1                                            L07975</t>
   </si>
@@ -298,13 +299,142 @@
   </si>
   <si>
     <t>Mid trim</t>
+  </si>
+  <si>
+    <t>What I should see</t>
+  </si>
+  <si>
+    <t>Full Scannable Order Number</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Frame Width</t>
+  </si>
+  <si>
+    <t>Frame Height</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>Schedule Date</t>
+  </si>
+  <si>
+    <t>Destination</t>
+  </si>
+  <si>
+    <t>R-SO-5106483-1-1</t>
+  </si>
+  <si>
+    <t>VPD</t>
+  </si>
+  <si>
+    <t>Bronze/White</t>
+  </si>
+  <si>
+    <t>Rebs</t>
+  </si>
+  <si>
+    <t>Cville</t>
+  </si>
+  <si>
+    <t>R-SO-5106483-1-2</t>
+  </si>
+  <si>
+    <t>Pandas df</t>
+  </si>
+  <si>
+    <t>unsortedOrders</t>
+  </si>
+  <si>
+    <t>list(OrderInfo)</t>
+  </si>
+  <si>
+    <t>@dataclass</t>
+  </si>
+  <si>
+    <t>class OrderInfo:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    fullOrderNum: str</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    component: str</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    length: float</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    position: int</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    color: str</t>
+  </si>
+  <si>
+    <t>class OrderSet:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    order1: OrderInfo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    order2: OrderInfo</t>
+  </si>
+  <si>
+    <t>class OrderList:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    profileID: str</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    orders: list[OrderSet] = field(default_factory=list)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    highestUsedPosition: int = 0</t>
+  </si>
+  <si>
+    <t>orderLists</t>
+  </si>
+  <si>
+    <t>list(OrderList)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    orders: list[OrderSet] </t>
+  </si>
+  <si>
+    <t>]</t>
+  </si>
+  <si>
+    <t>[   order1, order2</t>
+  </si>
+  <si>
+    <t>order1, order2 (OrderInfo)</t>
+  </si>
+  <si>
+    <t>tempProfileID = "VPDPAH2"</t>
+  </si>
+  <si>
+    <t>tempOrder1</t>
+  </si>
+  <si>
+    <t>(6483-1-1)</t>
+  </si>
+  <si>
+    <t>1,2</t>
+  </si>
+  <si>
+    <t>White/White</t>
+  </si>
+  <si>
+    <t>3, [ ]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -326,8 +456,32 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -382,8 +536,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -471,11 +637,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -496,18 +699,33 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1225,24 +1443,24 @@
       <c r="R4" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="S4" s="20" t="s">
+      <c r="S4" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="T4" s="20"/>
-      <c r="U4" s="20"/>
-      <c r="V4" s="20"/>
+      <c r="T4" s="22"/>
+      <c r="U4" s="22"/>
+      <c r="V4" s="22"/>
       <c r="W4" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Z4" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="AA4" s="21" t="s">
+      <c r="AA4" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="AB4" s="21"/>
-      <c r="AC4" s="21"/>
-      <c r="AD4" s="21"/>
+      <c r="AB4" s="23"/>
+      <c r="AC4" s="23"/>
+      <c r="AD4" s="23"/>
       <c r="AE4" s="7" t="s">
         <v>28</v>
       </c>
@@ -1250,12 +1468,12 @@
       <c r="AH4" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="AI4" s="20" t="s">
+      <c r="AI4" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="AJ4" s="20"/>
-      <c r="AK4" s="20"/>
-      <c r="AL4" s="20"/>
+      <c r="AJ4" s="22"/>
+      <c r="AK4" s="22"/>
+      <c r="AL4" s="22"/>
       <c r="AM4" s="2" t="s">
         <v>29</v>
       </c>
@@ -1589,24 +1807,24 @@
       <c r="R9" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="S9" s="20" t="s">
+      <c r="S9" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="T9" s="20"/>
-      <c r="U9" s="20"/>
-      <c r="V9" s="20"/>
+      <c r="T9" s="22"/>
+      <c r="U9" s="22"/>
+      <c r="V9" s="22"/>
       <c r="W9" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Z9" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="AA9" s="21" t="s">
+      <c r="AA9" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="AB9" s="21"/>
-      <c r="AC9" s="21"/>
-      <c r="AD9" s="21"/>
+      <c r="AB9" s="23"/>
+      <c r="AC9" s="23"/>
+      <c r="AD9" s="23"/>
       <c r="AE9" s="7" t="s">
         <v>28</v>
       </c>
@@ -1614,12 +1832,12 @@
       <c r="AH9" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AI9" s="20" t="s">
+      <c r="AI9" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="AJ9" s="20"/>
-      <c r="AK9" s="20"/>
-      <c r="AL9" s="20"/>
+      <c r="AJ9" s="22"/>
+      <c r="AK9" s="22"/>
+      <c r="AL9" s="22"/>
       <c r="AM9" s="2" t="s">
         <v>29</v>
       </c>
@@ -1909,24 +2127,24 @@
       <c r="R13" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="S13" s="20" t="s">
+      <c r="S13" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="T13" s="20"/>
-      <c r="U13" s="20"/>
-      <c r="V13" s="20"/>
+      <c r="T13" s="22"/>
+      <c r="U13" s="22"/>
+      <c r="V13" s="22"/>
       <c r="W13" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Z13" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="AA13" s="21" t="s">
+      <c r="AA13" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="AB13" s="21"/>
-      <c r="AC13" s="21"/>
-      <c r="AD13" s="21"/>
+      <c r="AB13" s="23"/>
+      <c r="AC13" s="23"/>
+      <c r="AD13" s="23"/>
       <c r="AE13" s="7" t="s">
         <v>28</v>
       </c>
@@ -2087,12 +2305,12 @@
       <c r="AH15" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AI15" s="20" t="s">
+      <c r="AI15" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="AJ15" s="20"/>
-      <c r="AK15" s="20"/>
-      <c r="AL15" s="20"/>
+      <c r="AJ15" s="22"/>
+      <c r="AK15" s="22"/>
+      <c r="AL15" s="22"/>
       <c r="AM15" s="2" t="s">
         <v>29</v>
       </c>
@@ -2253,24 +2471,24 @@
       <c r="R18" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="S18" s="20" t="s">
+      <c r="S18" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="T18" s="20"/>
-      <c r="U18" s="20"/>
-      <c r="V18" s="20"/>
+      <c r="T18" s="22"/>
+      <c r="U18" s="22"/>
+      <c r="V18" s="22"/>
       <c r="W18" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Z18" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="AA18" s="21" t="s">
+      <c r="AA18" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="AB18" s="21"/>
-      <c r="AC18" s="21"/>
-      <c r="AD18" s="21"/>
+      <c r="AB18" s="23"/>
+      <c r="AC18" s="23"/>
+      <c r="AD18" s="23"/>
       <c r="AE18" s="7" t="s">
         <v>28</v>
       </c>
@@ -2495,12 +2713,12 @@
       <c r="AH21" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="AI21" s="20" t="s">
+      <c r="AI21" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="AJ21" s="20"/>
-      <c r="AK21" s="20"/>
-      <c r="AL21" s="20"/>
+      <c r="AJ21" s="22"/>
+      <c r="AK21" s="22"/>
+      <c r="AL21" s="22"/>
       <c r="AM21" s="2" t="s">
         <v>29</v>
       </c>
@@ -2597,12 +2815,12 @@
       <c r="Z23" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AA23" s="20" t="s">
+      <c r="AA23" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="AB23" s="20"/>
-      <c r="AC23" s="20"/>
-      <c r="AD23" s="20"/>
+      <c r="AB23" s="22"/>
+      <c r="AC23" s="22"/>
+      <c r="AD23" s="22"/>
       <c r="AE23" s="2" t="s">
         <v>28</v>
       </c>
@@ -2840,12 +3058,12 @@
       <c r="Z27" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="AA27" s="20" t="s">
+      <c r="AA27" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="AB27" s="20"/>
-      <c r="AC27" s="20"/>
-      <c r="AD27" s="20"/>
+      <c r="AB27" s="22"/>
+      <c r="AC27" s="22"/>
+      <c r="AD27" s="22"/>
       <c r="AE27" s="2" t="s">
         <v>28</v>
       </c>
@@ -3992,12 +4210,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="AA23:AD23"/>
-    <mergeCell ref="AA27:AD27"/>
-    <mergeCell ref="AA4:AD4"/>
-    <mergeCell ref="AA9:AD9"/>
-    <mergeCell ref="AA13:AD13"/>
-    <mergeCell ref="AA18:AD18"/>
     <mergeCell ref="S4:V4"/>
     <mergeCell ref="S9:V9"/>
     <mergeCell ref="S13:V13"/>
@@ -4006,6 +4218,12 @@
     <mergeCell ref="AI4:AL4"/>
     <mergeCell ref="AI9:AL9"/>
     <mergeCell ref="AI15:AL15"/>
+    <mergeCell ref="AA23:AD23"/>
+    <mergeCell ref="AA27:AD27"/>
+    <mergeCell ref="AA4:AD4"/>
+    <mergeCell ref="AA9:AD9"/>
+    <mergeCell ref="AA13:AD13"/>
+    <mergeCell ref="AA18:AD18"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4094,12 +4312,12 @@
       <c r="R2" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="S2" s="20" t="s">
+      <c r="S2" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="T2" s="20"/>
-      <c r="U2" s="20"/>
-      <c r="V2" s="20"/>
+      <c r="T2" s="22"/>
+      <c r="U2" s="22"/>
+      <c r="V2" s="22"/>
       <c r="W2" s="2" t="s">
         <v>26</v>
       </c>
@@ -4259,12 +4477,12 @@
       <c r="Z4" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="AA4" s="21" t="s">
+      <c r="AA4" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="AB4" s="21"/>
-      <c r="AC4" s="21"/>
-      <c r="AD4" s="21"/>
+      <c r="AB4" s="23"/>
+      <c r="AC4" s="23"/>
+      <c r="AD4" s="23"/>
       <c r="AE4" s="7" t="s">
         <v>28</v>
       </c>
@@ -4313,11 +4531,11 @@
       <c r="P5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="V5" s="20" t="s">
+      <c r="V5" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="W5" s="20"/>
-      <c r="X5" s="20"/>
+      <c r="W5" s="22"/>
+      <c r="X5" s="22"/>
       <c r="Y5">
         <v>49</v>
       </c>
@@ -4338,18 +4556,18 @@
       <c r="AI5" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AJ5" s="22" t="s">
+      <c r="AJ5" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="AK5" s="22"/>
+      <c r="AK5" s="21"/>
       <c r="AL5" s="12" t="s">
         <v>81</v>
       </c>
       <c r="AM5" s="12"/>
-      <c r="AN5" s="22" t="s">
+      <c r="AN5" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="AO5" s="22"/>
+      <c r="AO5" s="21"/>
       <c r="AP5" s="12" t="s">
         <v>83</v>
       </c>
@@ -4470,17 +4688,17 @@
       <c r="AI7" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="AJ7" s="20" t="s">
+      <c r="AJ7" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="AK7" s="20"/>
+      <c r="AK7" s="22"/>
       <c r="AL7">
         <v>1</v>
       </c>
-      <c r="AN7" s="20" t="s">
+      <c r="AN7" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="AO7" s="20"/>
+      <c r="AO7" s="22"/>
       <c r="AP7">
         <v>49</v>
       </c>
@@ -4524,12 +4742,12 @@
       <c r="R8" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="S8" s="20" t="s">
+      <c r="S8" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="T8" s="20"/>
-      <c r="U8" s="20"/>
-      <c r="V8" s="20"/>
+      <c r="T8" s="22"/>
+      <c r="U8" s="22"/>
+      <c r="V8" s="22"/>
       <c r="W8" s="2" t="s">
         <v>26</v>
       </c>
@@ -4537,18 +4755,18 @@
       <c r="AI8" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="AJ8" s="23" t="s">
+      <c r="AJ8" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="AK8" s="23"/>
+      <c r="AK8" s="20"/>
       <c r="AL8" s="18">
         <v>1</v>
       </c>
       <c r="AM8" s="18"/>
-      <c r="AN8" s="23" t="s">
+      <c r="AN8" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="AO8" s="23"/>
+      <c r="AO8" s="20"/>
       <c r="AP8" s="18">
         <v>49</v>
       </c>
@@ -4627,12 +4845,12 @@
       <c r="Z9" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="AA9" s="21" t="s">
+      <c r="AA9" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="AB9" s="21"/>
-      <c r="AC9" s="21"/>
-      <c r="AD9" s="21"/>
+      <c r="AB9" s="23"/>
+      <c r="AC9" s="23"/>
+      <c r="AD9" s="23"/>
       <c r="AE9" s="7" t="s">
         <v>28</v>
       </c>
@@ -4761,11 +4979,11 @@
       <c r="P11" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="V11" s="20" t="s">
+      <c r="V11" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="W11" s="20"/>
-      <c r="X11" s="20"/>
+      <c r="W11" s="22"/>
+      <c r="X11" s="22"/>
       <c r="Y11">
         <v>49</v>
       </c>
@@ -4785,18 +5003,18 @@
       <c r="AI11" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AJ11" s="22" t="s">
+      <c r="AJ11" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="AK11" s="22"/>
+      <c r="AK11" s="21"/>
       <c r="AL11" s="12" t="s">
         <v>81</v>
       </c>
       <c r="AM11" s="12"/>
-      <c r="AN11" s="22" t="s">
+      <c r="AN11" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="AO11" s="22"/>
+      <c r="AO11" s="21"/>
       <c r="AP11" s="12" t="s">
         <v>83</v>
       </c>
@@ -4888,12 +5106,12 @@
       <c r="Z13" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="AA13" s="21" t="s">
+      <c r="AA13" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="AB13" s="21"/>
-      <c r="AC13" s="21"/>
-      <c r="AD13" s="21"/>
+      <c r="AB13" s="23"/>
+      <c r="AC13" s="23"/>
+      <c r="AD13" s="23"/>
       <c r="AE13" s="7" t="s">
         <v>28</v>
       </c>
@@ -4901,18 +5119,18 @@
       <c r="AI13" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="AJ13" s="23" t="s">
+      <c r="AJ13" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="AK13" s="23"/>
+      <c r="AK13" s="20"/>
       <c r="AL13" s="18">
         <v>1</v>
       </c>
       <c r="AM13" s="18"/>
-      <c r="AN13" s="23" t="s">
+      <c r="AN13" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="AO13" s="23"/>
+      <c r="AO13" s="20"/>
       <c r="AP13" s="18">
         <v>49</v>
       </c>
@@ -4972,12 +5190,12 @@
       <c r="R14" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="S14" s="20" t="s">
+      <c r="S14" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="T14" s="20"/>
-      <c r="U14" s="20"/>
-      <c r="V14" s="20"/>
+      <c r="T14" s="22"/>
+      <c r="U14" s="22"/>
+      <c r="V14" s="22"/>
       <c r="W14" s="2" t="s">
         <v>26</v>
       </c>
@@ -4997,10 +5215,10 @@
       <c r="AF14" s="2"/>
       <c r="AG14" s="2"/>
       <c r="AI14" s="2"/>
-      <c r="AJ14" s="20"/>
-      <c r="AK14" s="20"/>
-      <c r="AN14" s="20"/>
-      <c r="AO14" s="20"/>
+      <c r="AJ14" s="22"/>
+      <c r="AK14" s="22"/>
+      <c r="AN14" s="22"/>
+      <c r="AO14" s="22"/>
     </row>
     <row r="15" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B15">
@@ -5146,18 +5364,18 @@
       <c r="AI16" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AJ16" s="22" t="s">
+      <c r="AJ16" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="AK16" s="22"/>
+      <c r="AK16" s="21"/>
       <c r="AL16" s="12" t="s">
         <v>81</v>
       </c>
       <c r="AM16" s="12"/>
-      <c r="AN16" s="22" t="s">
+      <c r="AN16" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="AO16" s="22"/>
+      <c r="AO16" s="21"/>
       <c r="AP16" s="12" t="s">
         <v>83</v>
       </c>
@@ -5212,11 +5430,11 @@
       <c r="P17" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="V17" s="20" t="s">
+      <c r="V17" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="W17" s="20"/>
-      <c r="X17" s="20"/>
+      <c r="W17" s="22"/>
+      <c r="X17" s="22"/>
       <c r="Y17">
         <v>49</v>
       </c>
@@ -5257,12 +5475,12 @@
       <c r="Z18" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="AA18" s="21" t="s">
+      <c r="AA18" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="AB18" s="21"/>
-      <c r="AC18" s="21"/>
-      <c r="AD18" s="21"/>
+      <c r="AB18" s="23"/>
+      <c r="AC18" s="23"/>
+      <c r="AD18" s="23"/>
       <c r="AE18" s="7" t="s">
         <v>28</v>
       </c>
@@ -5270,18 +5488,18 @@
       <c r="AI18" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="AJ18" s="23" t="s">
+      <c r="AJ18" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="AK18" s="23"/>
+      <c r="AK18" s="20"/>
       <c r="AL18" s="18">
         <v>1</v>
       </c>
       <c r="AM18" s="18"/>
-      <c r="AN18" s="23" t="s">
+      <c r="AN18" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="AO18" s="23"/>
+      <c r="AO18" s="20"/>
       <c r="AP18" s="18">
         <v>49</v>
       </c>
@@ -5399,12 +5617,12 @@
       <c r="R20" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="S20" s="20" t="s">
+      <c r="S20" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="T20" s="20"/>
-      <c r="U20" s="20"/>
-      <c r="V20" s="20"/>
+      <c r="T20" s="22"/>
+      <c r="U20" s="22"/>
+      <c r="V20" s="22"/>
       <c r="W20" s="2" t="s">
         <v>26</v>
       </c>
@@ -5425,18 +5643,18 @@
       <c r="AI20" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AJ20" s="22" t="s">
+      <c r="AJ20" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="AK20" s="22"/>
+      <c r="AK20" s="21"/>
       <c r="AL20" s="12" t="s">
         <v>81</v>
       </c>
       <c r="AM20" s="12"/>
-      <c r="AN20" s="22" t="s">
+      <c r="AN20" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="AO20" s="22"/>
+      <c r="AO20" s="21"/>
       <c r="AP20" s="12" t="s">
         <v>83</v>
       </c>
@@ -5585,18 +5803,18 @@
       <c r="AI22" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="AJ22" s="23" t="s">
+      <c r="AJ22" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="AK22" s="23"/>
+      <c r="AK22" s="20"/>
       <c r="AL22" s="18">
         <v>2</v>
       </c>
       <c r="AM22" s="18"/>
-      <c r="AN22" s="23" t="s">
+      <c r="AN22" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="AO22" s="23"/>
+      <c r="AO22" s="20"/>
       <c r="AP22" s="18">
         <v>2</v>
       </c>
@@ -5637,11 +5855,11 @@
       <c r="I23">
         <v>21</v>
       </c>
-      <c r="V23" s="20" t="s">
+      <c r="V23" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="W23" s="20"/>
-      <c r="X23" s="20"/>
+      <c r="W23" s="22"/>
+      <c r="X23" s="22"/>
       <c r="Y23">
         <v>49</v>
       </c>
@@ -5692,18 +5910,18 @@
       <c r="AI24" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AJ24" s="22" t="s">
+      <c r="AJ24" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="AK24" s="22"/>
+      <c r="AK24" s="21"/>
       <c r="AL24" s="12" t="s">
         <v>81</v>
       </c>
       <c r="AM24" s="12"/>
-      <c r="AN24" s="22" t="s">
+      <c r="AN24" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="AO24" s="22"/>
+      <c r="AO24" s="21"/>
       <c r="AP24" s="12" t="s">
         <v>83</v>
       </c>
@@ -5788,12 +6006,12 @@
       <c r="R26" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="S26" s="20" t="s">
+      <c r="S26" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="T26" s="20"/>
-      <c r="U26" s="20"/>
-      <c r="V26" s="20"/>
+      <c r="T26" s="22"/>
+      <c r="U26" s="22"/>
+      <c r="V26" s="22"/>
       <c r="W26" s="2" t="s">
         <v>28</v>
       </c>
@@ -5801,18 +6019,18 @@
       <c r="AI26" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="AJ26" s="23" t="s">
+      <c r="AJ26" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="AK26" s="23"/>
+      <c r="AK26" s="20"/>
       <c r="AL26" s="18">
         <v>2</v>
       </c>
       <c r="AM26" s="18"/>
-      <c r="AN26" s="23" t="s">
+      <c r="AN26" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="AO26" s="23"/>
+      <c r="AO26" s="20"/>
       <c r="AP26" s="18">
         <v>2</v>
       </c>
@@ -5982,29 +6200,29 @@
       <c r="P29" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="V29" s="20" t="s">
+      <c r="V29" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="W29" s="20"/>
-      <c r="X29" s="20"/>
+      <c r="W29" s="22"/>
+      <c r="X29" s="22"/>
       <c r="Y29" s="10">
         <v>2</v>
       </c>
       <c r="AI29" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AJ29" s="22" t="s">
+      <c r="AJ29" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="AK29" s="22"/>
+      <c r="AK29" s="21"/>
       <c r="AL29" s="12" t="s">
         <v>81</v>
       </c>
       <c r="AM29" s="12"/>
-      <c r="AN29" s="22" t="s">
+      <c r="AN29" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="AO29" s="22"/>
+      <c r="AO29" s="21"/>
       <c r="AP29" s="12" t="s">
         <v>83</v>
       </c>
@@ -6112,17 +6330,17 @@
       <c r="AI31" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="AJ31" s="20" t="s">
+      <c r="AJ31" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="AK31" s="20"/>
+      <c r="AK31" s="22"/>
       <c r="AL31">
         <v>3</v>
       </c>
-      <c r="AN31" s="20" t="s">
+      <c r="AN31" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="AO31" s="20"/>
+      <c r="AO31" s="22"/>
       <c r="AP31">
         <v>4</v>
       </c>
@@ -6182,12 +6400,12 @@
       <c r="R32" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="S32" s="20" t="s">
+      <c r="S32" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="T32" s="20"/>
-      <c r="U32" s="20"/>
-      <c r="V32" s="20"/>
+      <c r="T32" s="22"/>
+      <c r="U32" s="22"/>
+      <c r="V32" s="22"/>
       <c r="W32" s="2" t="s">
         <v>28</v>
       </c>
@@ -6195,17 +6413,17 @@
       <c r="AI32" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="AJ32" s="20" t="s">
+      <c r="AJ32" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="AK32" s="20"/>
+      <c r="AK32" s="22"/>
       <c r="AL32">
         <v>3</v>
       </c>
-      <c r="AN32" s="20" t="s">
+      <c r="AN32" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="AO32" s="20"/>
+      <c r="AO32" s="22"/>
       <c r="AP32">
         <v>4</v>
       </c>
@@ -6268,17 +6486,17 @@
       <c r="AI33" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="AJ33" s="20" t="s">
+      <c r="AJ33" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="AK33" s="20"/>
+      <c r="AK33" s="22"/>
       <c r="AL33">
         <v>5</v>
       </c>
-      <c r="AN33" s="20" t="s">
+      <c r="AN33" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="AO33" s="20"/>
+      <c r="AO33" s="22"/>
       <c r="AP33">
         <v>6</v>
       </c>
@@ -6360,18 +6578,18 @@
       <c r="AI34" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="AJ34" s="23" t="s">
+      <c r="AJ34" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="AK34" s="23"/>
+      <c r="AK34" s="20"/>
       <c r="AL34" s="18">
         <v>5</v>
       </c>
       <c r="AM34" s="18"/>
-      <c r="AN34" s="23" t="s">
+      <c r="AN34" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="AO34" s="23"/>
+      <c r="AO34" s="20"/>
       <c r="AP34" s="18">
         <v>6</v>
       </c>
@@ -6428,11 +6646,11 @@
       <c r="P35" t="s">
         <v>29</v>
       </c>
-      <c r="V35" s="20" t="s">
+      <c r="V35" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="W35" s="20"/>
-      <c r="X35" s="20"/>
+      <c r="W35" s="22"/>
+      <c r="X35" s="22"/>
       <c r="Y35" s="10">
         <v>2</v>
       </c>
@@ -6501,18 +6719,18 @@
       <c r="AI37" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AJ37" s="22" t="s">
+      <c r="AJ37" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="AK37" s="22"/>
+      <c r="AK37" s="21"/>
       <c r="AL37" s="12" t="s">
         <v>81</v>
       </c>
       <c r="AM37" s="12"/>
-      <c r="AN37" s="22" t="s">
+      <c r="AN37" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="AO37" s="22"/>
+      <c r="AO37" s="21"/>
       <c r="AP37" s="12" t="s">
         <v>83</v>
       </c>
@@ -6528,12 +6746,12 @@
       <c r="R38" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="S38" s="20" t="s">
+      <c r="S38" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="T38" s="20"/>
-      <c r="U38" s="20"/>
-      <c r="V38" s="20"/>
+      <c r="T38" s="22"/>
+      <c r="U38" s="22"/>
+      <c r="V38" s="22"/>
       <c r="W38" s="2" t="s">
         <v>29</v>
       </c>
@@ -6584,18 +6802,18 @@
       <c r="AI39" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="AJ39" s="23" t="s">
+      <c r="AJ39" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="AK39" s="23"/>
+      <c r="AK39" s="20"/>
       <c r="AL39" s="18">
         <v>3</v>
       </c>
       <c r="AM39" s="18"/>
-      <c r="AN39" s="23" t="s">
+      <c r="AN39" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="AO39" s="23"/>
+      <c r="AO39" s="20"/>
       <c r="AP39" s="18">
         <v>4</v>
       </c>
@@ -6706,29 +6924,29 @@
       <c r="P42" t="s">
         <v>43</v>
       </c>
-      <c r="V42" s="20" t="s">
+      <c r="V42" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="W42" s="20"/>
-      <c r="X42" s="20"/>
+      <c r="W42" s="22"/>
+      <c r="X42" s="22"/>
       <c r="Y42">
         <v>6</v>
       </c>
       <c r="AI42" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AJ42" s="22" t="s">
+      <c r="AJ42" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="AK42" s="22"/>
+      <c r="AK42" s="21"/>
       <c r="AL42" s="12" t="s">
         <v>81</v>
       </c>
       <c r="AM42" s="12"/>
-      <c r="AN42" s="22" t="s">
+      <c r="AN42" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="AO42" s="22"/>
+      <c r="AO42" s="21"/>
       <c r="AP42" s="12" t="s">
         <v>83</v>
       </c>
@@ -6768,18 +6986,18 @@
       <c r="AI44" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="AJ44" s="23" t="s">
+      <c r="AJ44" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="AK44" s="23"/>
+      <c r="AK44" s="20"/>
       <c r="AL44" s="18">
         <v>3</v>
       </c>
       <c r="AM44" s="18"/>
-      <c r="AN44" s="23" t="s">
+      <c r="AN44" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="AO44" s="23"/>
+      <c r="AO44" s="20"/>
       <c r="AP44" s="18">
         <v>4</v>
       </c>
@@ -6813,12 +7031,12 @@
       <c r="R45" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="S45" s="20" t="s">
+      <c r="S45" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="T45" s="20"/>
-      <c r="U45" s="20"/>
-      <c r="V45" s="20"/>
+      <c r="T45" s="22"/>
+      <c r="U45" s="22"/>
+      <c r="V45" s="22"/>
       <c r="W45" s="2" t="s">
         <v>29</v>
       </c>
@@ -6863,18 +7081,18 @@
       <c r="AI46" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AJ46" s="22" t="s">
+      <c r="AJ46" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="AK46" s="22"/>
+      <c r="AK46" s="21"/>
       <c r="AL46" s="12" t="s">
         <v>81</v>
       </c>
       <c r="AM46" s="12"/>
-      <c r="AN46" s="22" t="s">
+      <c r="AN46" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="AO46" s="22"/>
+      <c r="AO46" s="21"/>
       <c r="AP46" s="12" t="s">
         <v>83</v>
       </c>
@@ -6958,18 +7176,18 @@
       <c r="AI48" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="AJ48" s="23" t="s">
+      <c r="AJ48" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="AK48" s="23"/>
+      <c r="AK48" s="20"/>
       <c r="AL48" s="18">
         <v>5</v>
       </c>
       <c r="AM48" s="18"/>
-      <c r="AN48" s="23" t="s">
+      <c r="AN48" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="AO48" s="23"/>
+      <c r="AO48" s="20"/>
       <c r="AP48" s="18">
         <v>6</v>
       </c>
@@ -7000,11 +7218,11 @@
       <c r="P49" t="s">
         <v>43</v>
       </c>
-      <c r="V49" s="20" t="s">
+      <c r="V49" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="W49" s="20"/>
-      <c r="X49" s="20"/>
+      <c r="W49" s="22"/>
+      <c r="X49" s="22"/>
       <c r="Y49">
         <v>6</v>
       </c>
@@ -7065,12 +7283,12 @@
       <c r="R52" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="S52" s="20" t="s">
+      <c r="S52" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="T52" s="20"/>
-      <c r="U52" s="20"/>
-      <c r="V52" s="20"/>
+      <c r="T52" s="22"/>
+      <c r="U52" s="22"/>
+      <c r="V52" s="22"/>
       <c r="W52" s="2" t="s">
         <v>29</v>
       </c>
@@ -7194,11 +7412,11 @@
       <c r="P56" t="s">
         <v>43</v>
       </c>
-      <c r="V56" s="20" t="s">
+      <c r="V56" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="W56" s="20"/>
-      <c r="X56" s="20"/>
+      <c r="W56" s="22"/>
+      <c r="X56" s="22"/>
       <c r="Y56">
         <v>6</v>
       </c>
@@ -7241,12 +7459,12 @@
       <c r="R59" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="S59" s="20" t="s">
+      <c r="S59" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="T59" s="20"/>
-      <c r="U59" s="20"/>
-      <c r="V59" s="20"/>
+      <c r="T59" s="22"/>
+      <c r="U59" s="22"/>
+      <c r="V59" s="22"/>
       <c r="W59" s="2" t="s">
         <v>29</v>
       </c>
@@ -7369,11 +7587,11 @@
       <c r="Y62" s="10"/>
     </row>
     <row r="63" spans="12:25" x14ac:dyDescent="0.25">
-      <c r="V63" s="20" t="s">
+      <c r="V63" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="W63" s="20"/>
-      <c r="X63" s="20"/>
+      <c r="W63" s="22"/>
+      <c r="X63" s="22"/>
       <c r="Y63">
         <v>4</v>
       </c>
@@ -7740,43 +7958,23 @@
     </row>
   </sheetData>
   <mergeCells count="70">
-    <mergeCell ref="AJ44:AK44"/>
-    <mergeCell ref="AN44:AO44"/>
-    <mergeCell ref="AJ46:AK46"/>
-    <mergeCell ref="AN46:AO46"/>
-    <mergeCell ref="AJ48:AK48"/>
-    <mergeCell ref="AN48:AO48"/>
-    <mergeCell ref="AJ42:AK42"/>
-    <mergeCell ref="AN42:AO42"/>
-    <mergeCell ref="AJ34:AK34"/>
-    <mergeCell ref="AN34:AO34"/>
-    <mergeCell ref="AJ37:AK37"/>
-    <mergeCell ref="AN37:AO37"/>
-    <mergeCell ref="AJ39:AK39"/>
-    <mergeCell ref="AN39:AO39"/>
-    <mergeCell ref="AJ31:AK31"/>
-    <mergeCell ref="AN31:AO31"/>
-    <mergeCell ref="AJ32:AK32"/>
-    <mergeCell ref="AN32:AO32"/>
-    <mergeCell ref="AJ33:AK33"/>
-    <mergeCell ref="AN33:AO33"/>
-    <mergeCell ref="AJ24:AK24"/>
-    <mergeCell ref="AN24:AO24"/>
-    <mergeCell ref="AJ26:AK26"/>
-    <mergeCell ref="AN26:AO26"/>
-    <mergeCell ref="AJ29:AK29"/>
-    <mergeCell ref="AN29:AO29"/>
-    <mergeCell ref="AJ18:AK18"/>
-    <mergeCell ref="AN18:AO18"/>
-    <mergeCell ref="AJ20:AK20"/>
-    <mergeCell ref="AN20:AO20"/>
-    <mergeCell ref="AJ22:AK22"/>
-    <mergeCell ref="AN22:AO22"/>
-    <mergeCell ref="AN13:AO13"/>
-    <mergeCell ref="AJ14:AK14"/>
-    <mergeCell ref="AN14:AO14"/>
-    <mergeCell ref="AJ16:AK16"/>
-    <mergeCell ref="AN16:AO16"/>
+    <mergeCell ref="S2:V2"/>
+    <mergeCell ref="AA4:AD4"/>
+    <mergeCell ref="S38:V38"/>
+    <mergeCell ref="S8:V8"/>
+    <mergeCell ref="AA9:AD9"/>
+    <mergeCell ref="V29:X29"/>
+    <mergeCell ref="S14:V14"/>
+    <mergeCell ref="AA13:AD13"/>
+    <mergeCell ref="S20:V20"/>
+    <mergeCell ref="AA18:AD18"/>
+    <mergeCell ref="S59:V59"/>
+    <mergeCell ref="V35:X35"/>
+    <mergeCell ref="V42:X42"/>
+    <mergeCell ref="V49:X49"/>
+    <mergeCell ref="V56:X56"/>
+    <mergeCell ref="S45:V45"/>
+    <mergeCell ref="S52:V52"/>
     <mergeCell ref="V63:X63"/>
     <mergeCell ref="AJ5:AK5"/>
     <mergeCell ref="AN5:AO5"/>
@@ -7793,24 +7991,1093 @@
     <mergeCell ref="V11:X11"/>
     <mergeCell ref="V17:X17"/>
     <mergeCell ref="V23:X23"/>
-    <mergeCell ref="S59:V59"/>
-    <mergeCell ref="V35:X35"/>
-    <mergeCell ref="V42:X42"/>
-    <mergeCell ref="V49:X49"/>
-    <mergeCell ref="V56:X56"/>
-    <mergeCell ref="S45:V45"/>
-    <mergeCell ref="S52:V52"/>
-    <mergeCell ref="S2:V2"/>
-    <mergeCell ref="AA4:AD4"/>
-    <mergeCell ref="S38:V38"/>
-    <mergeCell ref="S8:V8"/>
-    <mergeCell ref="AA9:AD9"/>
-    <mergeCell ref="V29:X29"/>
-    <mergeCell ref="S14:V14"/>
-    <mergeCell ref="AA13:AD13"/>
-    <mergeCell ref="S20:V20"/>
-    <mergeCell ref="AA18:AD18"/>
+    <mergeCell ref="AN13:AO13"/>
+    <mergeCell ref="AJ14:AK14"/>
+    <mergeCell ref="AN14:AO14"/>
+    <mergeCell ref="AJ16:AK16"/>
+    <mergeCell ref="AN16:AO16"/>
+    <mergeCell ref="AJ18:AK18"/>
+    <mergeCell ref="AN18:AO18"/>
+    <mergeCell ref="AJ20:AK20"/>
+    <mergeCell ref="AN20:AO20"/>
+    <mergeCell ref="AJ22:AK22"/>
+    <mergeCell ref="AN22:AO22"/>
+    <mergeCell ref="AJ24:AK24"/>
+    <mergeCell ref="AN24:AO24"/>
+    <mergeCell ref="AJ26:AK26"/>
+    <mergeCell ref="AN26:AO26"/>
+    <mergeCell ref="AJ29:AK29"/>
+    <mergeCell ref="AN29:AO29"/>
+    <mergeCell ref="AJ31:AK31"/>
+    <mergeCell ref="AN31:AO31"/>
+    <mergeCell ref="AJ32:AK32"/>
+    <mergeCell ref="AN32:AO32"/>
+    <mergeCell ref="AJ33:AK33"/>
+    <mergeCell ref="AN33:AO33"/>
+    <mergeCell ref="AJ42:AK42"/>
+    <mergeCell ref="AN42:AO42"/>
+    <mergeCell ref="AJ34:AK34"/>
+    <mergeCell ref="AN34:AO34"/>
+    <mergeCell ref="AJ37:AK37"/>
+    <mergeCell ref="AN37:AO37"/>
+    <mergeCell ref="AJ39:AK39"/>
+    <mergeCell ref="AN39:AO39"/>
+    <mergeCell ref="AJ44:AK44"/>
+    <mergeCell ref="AN44:AO44"/>
+    <mergeCell ref="AJ46:AK46"/>
+    <mergeCell ref="AN46:AO46"/>
+    <mergeCell ref="AJ48:AK48"/>
+    <mergeCell ref="AN48:AO48"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D31D181-2758-43CB-B29A-A87F826596E0}">
+  <dimension ref="A3:Q52"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" customWidth="1"/>
+    <col min="2" max="2" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23" customWidth="1"/>
+    <col min="14" max="14" width="1.5703125" customWidth="1"/>
+    <col min="15" max="15" width="18.140625" customWidth="1"/>
+    <col min="16" max="16" width="1.42578125" customWidth="1"/>
+    <col min="17" max="17" width="45.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>104</v>
+      </c>
+      <c r="M7" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="O7" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q7" s="27" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="F8" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="H8" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="I8" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="M8" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="O8" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q8" s="30" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" t="s">
+        <v>99</v>
+      </c>
+      <c r="D9">
+        <v>71.5</v>
+      </c>
+      <c r="E9">
+        <v>95.5</v>
+      </c>
+      <c r="F9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G9" t="s">
+        <v>101</v>
+      </c>
+      <c r="H9" s="26">
+        <v>46091</v>
+      </c>
+      <c r="I9" t="s">
+        <v>102</v>
+      </c>
+      <c r="M9" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="O9" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q9" s="28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" t="s">
+        <v>99</v>
+      </c>
+      <c r="D10">
+        <v>71.5</v>
+      </c>
+      <c r="E10">
+        <v>95.5</v>
+      </c>
+      <c r="F10" t="s">
+        <v>100</v>
+      </c>
+      <c r="G10" t="s">
+        <v>101</v>
+      </c>
+      <c r="H10" s="26">
+        <v>46091</v>
+      </c>
+      <c r="I10" t="s">
+        <v>102</v>
+      </c>
+      <c r="M10" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="O10" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q10" s="28" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M11" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q11" s="28" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M12" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q12" s="29" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M13" s="29" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>106</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="C17" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="E17" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="F17" s="29" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>0</v>
+      </c>
+      <c r="B18" t="s">
+        <v>98</v>
+      </c>
+      <c r="C18" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18">
+        <v>35.561999999999998</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>1</v>
+      </c>
+      <c r="B19" t="s">
+        <v>98</v>
+      </c>
+      <c r="C19" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19">
+        <v>92.875</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>2</v>
+      </c>
+      <c r="B20" t="s">
+        <v>98</v>
+      </c>
+      <c r="C20" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20">
+        <v>35.561999999999998</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>3</v>
+      </c>
+      <c r="B21" t="s">
+        <v>98</v>
+      </c>
+      <c r="C21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21">
+        <v>92.875</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
+        <v>103</v>
+      </c>
+      <c r="C22" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22">
+        <v>35.561999999999998</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>5</v>
+      </c>
+      <c r="B23" t="s">
+        <v>103</v>
+      </c>
+      <c r="C23" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23">
+        <v>92.875</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>6</v>
+      </c>
+      <c r="B24" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24" t="s">
+        <v>45</v>
+      </c>
+      <c r="D24">
+        <v>35.561999999999998</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>7</v>
+      </c>
+      <c r="B25" t="s">
+        <v>103</v>
+      </c>
+      <c r="C25" t="s">
+        <v>46</v>
+      </c>
+      <c r="D25">
+        <v>92.875</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>121</v>
+      </c>
+      <c r="D30" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>122</v>
+      </c>
+      <c r="B31" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="C31" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="D31" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="E31" t="s">
+        <v>120</v>
+      </c>
+      <c r="H31" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="33">
+        <v>0</v>
+      </c>
+      <c r="B32" t="s">
+        <v>100</v>
+      </c>
+      <c r="C32" t="s">
+        <v>71</v>
+      </c>
+      <c r="D32" s="32" t="s">
+        <v>132</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="H32" t="s">
+        <v>128</v>
+      </c>
+      <c r="I32" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>1</v>
+      </c>
+      <c r="B33" t="s">
+        <v>100</v>
+      </c>
+      <c r="C33" t="s">
+        <v>59</v>
+      </c>
+      <c r="D33" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>2</v>
+      </c>
+      <c r="B34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C34" t="s">
+        <v>72</v>
+      </c>
+      <c r="D34" s="32" t="s">
+        <v>132</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>3</v>
+      </c>
+      <c r="B35" t="s">
+        <v>100</v>
+      </c>
+      <c r="C35" t="s">
+        <v>63</v>
+      </c>
+      <c r="D35" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="33">
+        <v>4</v>
+      </c>
+      <c r="B36" t="s">
+        <v>100</v>
+      </c>
+      <c r="C36" t="s">
+        <v>20</v>
+      </c>
+      <c r="D36" s="32" t="s">
+        <v>132</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>5</v>
+      </c>
+      <c r="B37" t="s">
+        <v>100</v>
+      </c>
+      <c r="C37" t="s">
+        <v>61</v>
+      </c>
+      <c r="D37" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>6</v>
+      </c>
+      <c r="B38" t="s">
+        <v>100</v>
+      </c>
+      <c r="C38" t="s">
+        <v>73</v>
+      </c>
+      <c r="D38" s="32" t="s">
+        <v>132</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>7</v>
+      </c>
+      <c r="B39" t="s">
+        <v>100</v>
+      </c>
+      <c r="C39" t="s">
+        <v>65</v>
+      </c>
+      <c r="D39" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="34">
+        <v>8</v>
+      </c>
+      <c r="B40" t="s">
+        <v>100</v>
+      </c>
+      <c r="C40" t="s">
+        <v>74</v>
+      </c>
+      <c r="D40" s="32" t="s">
+        <v>132</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>9</v>
+      </c>
+      <c r="B41" t="s">
+        <v>100</v>
+      </c>
+      <c r="C41" t="s">
+        <v>76</v>
+      </c>
+      <c r="D41" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>11</v>
+      </c>
+      <c r="B43" t="s">
+        <v>131</v>
+      </c>
+      <c r="C43" t="s">
+        <v>71</v>
+      </c>
+      <c r="D43" s="32" t="s">
+        <v>132</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>12</v>
+      </c>
+      <c r="B44" t="s">
+        <v>131</v>
+      </c>
+      <c r="C44" t="s">
+        <v>59</v>
+      </c>
+      <c r="D44" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>13</v>
+      </c>
+      <c r="B45" t="s">
+        <v>131</v>
+      </c>
+      <c r="C45" t="s">
+        <v>72</v>
+      </c>
+      <c r="D45" s="32" t="s">
+        <v>132</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>14</v>
+      </c>
+      <c r="B46" t="s">
+        <v>131</v>
+      </c>
+      <c r="C46" t="s">
+        <v>63</v>
+      </c>
+      <c r="D46" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>131</v>
+      </c>
+      <c r="C47" t="s">
+        <v>20</v>
+      </c>
+      <c r="D47" s="32" t="s">
+        <v>132</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>16</v>
+      </c>
+      <c r="B48" t="s">
+        <v>131</v>
+      </c>
+      <c r="C48" t="s">
+        <v>61</v>
+      </c>
+      <c r="D48" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>17</v>
+      </c>
+      <c r="B49" t="s">
+        <v>131</v>
+      </c>
+      <c r="C49" t="s">
+        <v>73</v>
+      </c>
+      <c r="D49" s="32" t="s">
+        <v>132</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>18</v>
+      </c>
+      <c r="B50" t="s">
+        <v>131</v>
+      </c>
+      <c r="C50" t="s">
+        <v>65</v>
+      </c>
+      <c r="D50" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>19</v>
+      </c>
+      <c r="B51" t="s">
+        <v>131</v>
+      </c>
+      <c r="C51" t="s">
+        <v>74</v>
+      </c>
+      <c r="D51" s="32" t="s">
+        <v>132</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>20</v>
+      </c>
+      <c r="B52" t="s">
+        <v>131</v>
+      </c>
+      <c r="C52" t="s">
+        <v>76</v>
+      </c>
+      <c r="D52" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B23F7672-6133-4BFA-945E-284EF855777B}">
+  <dimension ref="A2:N33"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="1.7109375" customWidth="1"/>
+    <col min="12" max="12" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="1.5703125" customWidth="1"/>
+    <col min="14" max="14" width="45.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="E3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D4" t="s">
+        <v>125</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="J4" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="L4" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="N4" s="27" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J5" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="L5" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="N5" s="30" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="D6" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="J6" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="L6" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="N6" s="28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" t="s">
+        <v>125</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="J7" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="L7" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="N7" s="28" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J8" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="N8" s="28" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="D9" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="J9" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="N9" s="29" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" t="s">
+        <v>125</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="J10" s="29" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="D12" s="31" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" t="s">
+        <v>125</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="D15" s="31" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
+        <v>100</v>
+      </c>
+      <c r="C16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" t="s">
+        <v>125</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D18" s="31" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>5</v>
+      </c>
+      <c r="B19" t="s">
+        <v>100</v>
+      </c>
+      <c r="C19" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" t="s">
+        <v>125</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D21" s="31" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>6</v>
+      </c>
+      <c r="B22" t="s">
+        <v>100</v>
+      </c>
+      <c r="C22" t="s">
+        <v>73</v>
+      </c>
+      <c r="D22" t="s">
+        <v>125</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D24" s="31" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>7</v>
+      </c>
+      <c r="B25" t="s">
+        <v>100</v>
+      </c>
+      <c r="C25" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" t="s">
+        <v>125</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D27" s="31" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>8</v>
+      </c>
+      <c r="B28" t="s">
+        <v>100</v>
+      </c>
+      <c r="C28" t="s">
+        <v>74</v>
+      </c>
+      <c r="D28" t="s">
+        <v>125</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D30" s="31" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>9</v>
+      </c>
+      <c r="B31" t="s">
+        <v>100</v>
+      </c>
+      <c r="C31" t="s">
+        <v>76</v>
+      </c>
+      <c r="D31" t="s">
+        <v>125</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D33" s="31" t="s">
+        <v>124</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/VPD PO download generator/trying stuff business systems.xlsx
+++ b/VPD PO download generator/trying stuff business systems.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwa25\source\repos\VPD PO download generator\VPD PO download generator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6AFC98A-44CD-481B-8099-64F0EE14F9C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8ECCF37-B949-422D-BFEE-FD37EBD693C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{D51960FC-1269-4ACE-8C84-C0CBF6215B21}"/>
   </bookViews>
@@ -699,18 +699,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -726,6 +714,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1443,24 +1443,24 @@
       <c r="R4" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="S4" s="22" t="s">
+      <c r="S4" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="T4" s="22"/>
-      <c r="U4" s="22"/>
-      <c r="V4" s="22"/>
+      <c r="T4" s="31"/>
+      <c r="U4" s="31"/>
+      <c r="V4" s="31"/>
       <c r="W4" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Z4" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="AA4" s="23" t="s">
+      <c r="AA4" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="AB4" s="23"/>
-      <c r="AC4" s="23"/>
-      <c r="AD4" s="23"/>
+      <c r="AB4" s="32"/>
+      <c r="AC4" s="32"/>
+      <c r="AD4" s="32"/>
       <c r="AE4" s="7" t="s">
         <v>28</v>
       </c>
@@ -1468,12 +1468,12 @@
       <c r="AH4" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="AI4" s="22" t="s">
+      <c r="AI4" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="AJ4" s="22"/>
-      <c r="AK4" s="22"/>
-      <c r="AL4" s="22"/>
+      <c r="AJ4" s="31"/>
+      <c r="AK4" s="31"/>
+      <c r="AL4" s="31"/>
       <c r="AM4" s="2" t="s">
         <v>29</v>
       </c>
@@ -1807,24 +1807,24 @@
       <c r="R9" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="S9" s="22" t="s">
+      <c r="S9" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="T9" s="22"/>
-      <c r="U9" s="22"/>
-      <c r="V9" s="22"/>
+      <c r="T9" s="31"/>
+      <c r="U9" s="31"/>
+      <c r="V9" s="31"/>
       <c r="W9" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Z9" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="AA9" s="23" t="s">
+      <c r="AA9" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="AB9" s="23"/>
-      <c r="AC9" s="23"/>
-      <c r="AD9" s="23"/>
+      <c r="AB9" s="32"/>
+      <c r="AC9" s="32"/>
+      <c r="AD9" s="32"/>
       <c r="AE9" s="7" t="s">
         <v>28</v>
       </c>
@@ -1832,12 +1832,12 @@
       <c r="AH9" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AI9" s="22" t="s">
+      <c r="AI9" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="AJ9" s="22"/>
-      <c r="AK9" s="22"/>
-      <c r="AL9" s="22"/>
+      <c r="AJ9" s="31"/>
+      <c r="AK9" s="31"/>
+      <c r="AL9" s="31"/>
       <c r="AM9" s="2" t="s">
         <v>29</v>
       </c>
@@ -2127,24 +2127,24 @@
       <c r="R13" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="S13" s="22" t="s">
+      <c r="S13" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="T13" s="22"/>
-      <c r="U13" s="22"/>
-      <c r="V13" s="22"/>
+      <c r="T13" s="31"/>
+      <c r="U13" s="31"/>
+      <c r="V13" s="31"/>
       <c r="W13" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Z13" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="AA13" s="23" t="s">
+      <c r="AA13" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="AB13" s="23"/>
-      <c r="AC13" s="23"/>
-      <c r="AD13" s="23"/>
+      <c r="AB13" s="32"/>
+      <c r="AC13" s="32"/>
+      <c r="AD13" s="32"/>
       <c r="AE13" s="7" t="s">
         <v>28</v>
       </c>
@@ -2305,12 +2305,12 @@
       <c r="AH15" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AI15" s="22" t="s">
+      <c r="AI15" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="AJ15" s="22"/>
-      <c r="AK15" s="22"/>
-      <c r="AL15" s="22"/>
+      <c r="AJ15" s="31"/>
+      <c r="AK15" s="31"/>
+      <c r="AL15" s="31"/>
       <c r="AM15" s="2" t="s">
         <v>29</v>
       </c>
@@ -2471,24 +2471,24 @@
       <c r="R18" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="S18" s="22" t="s">
+      <c r="S18" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="T18" s="22"/>
-      <c r="U18" s="22"/>
-      <c r="V18" s="22"/>
+      <c r="T18" s="31"/>
+      <c r="U18" s="31"/>
+      <c r="V18" s="31"/>
       <c r="W18" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Z18" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="AA18" s="23" t="s">
+      <c r="AA18" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="AB18" s="23"/>
-      <c r="AC18" s="23"/>
-      <c r="AD18" s="23"/>
+      <c r="AB18" s="32"/>
+      <c r="AC18" s="32"/>
+      <c r="AD18" s="32"/>
       <c r="AE18" s="7" t="s">
         <v>28</v>
       </c>
@@ -2713,12 +2713,12 @@
       <c r="AH21" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="AI21" s="22" t="s">
+      <c r="AI21" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="AJ21" s="22"/>
-      <c r="AK21" s="22"/>
-      <c r="AL21" s="22"/>
+      <c r="AJ21" s="31"/>
+      <c r="AK21" s="31"/>
+      <c r="AL21" s="31"/>
       <c r="AM21" s="2" t="s">
         <v>29</v>
       </c>
@@ -2815,12 +2815,12 @@
       <c r="Z23" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AA23" s="22" t="s">
+      <c r="AA23" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="AB23" s="22"/>
-      <c r="AC23" s="22"/>
-      <c r="AD23" s="22"/>
+      <c r="AB23" s="31"/>
+      <c r="AC23" s="31"/>
+      <c r="AD23" s="31"/>
       <c r="AE23" s="2" t="s">
         <v>28</v>
       </c>
@@ -3058,12 +3058,12 @@
       <c r="Z27" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="AA27" s="22" t="s">
+      <c r="AA27" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="AB27" s="22"/>
-      <c r="AC27" s="22"/>
-      <c r="AD27" s="22"/>
+      <c r="AB27" s="31"/>
+      <c r="AC27" s="31"/>
+      <c r="AD27" s="31"/>
       <c r="AE27" s="2" t="s">
         <v>28</v>
       </c>
@@ -4210,6 +4210,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="AA23:AD23"/>
+    <mergeCell ref="AA27:AD27"/>
+    <mergeCell ref="AA4:AD4"/>
+    <mergeCell ref="AA9:AD9"/>
+    <mergeCell ref="AA13:AD13"/>
+    <mergeCell ref="AA18:AD18"/>
     <mergeCell ref="S4:V4"/>
     <mergeCell ref="S9:V9"/>
     <mergeCell ref="S13:V13"/>
@@ -4218,12 +4224,6 @@
     <mergeCell ref="AI4:AL4"/>
     <mergeCell ref="AI9:AL9"/>
     <mergeCell ref="AI15:AL15"/>
-    <mergeCell ref="AA23:AD23"/>
-    <mergeCell ref="AA27:AD27"/>
-    <mergeCell ref="AA4:AD4"/>
-    <mergeCell ref="AA9:AD9"/>
-    <mergeCell ref="AA13:AD13"/>
-    <mergeCell ref="AA18:AD18"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4312,12 +4312,12 @@
       <c r="R2" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="S2" s="22" t="s">
+      <c r="S2" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="T2" s="22"/>
-      <c r="U2" s="22"/>
-      <c r="V2" s="22"/>
+      <c r="T2" s="31"/>
+      <c r="U2" s="31"/>
+      <c r="V2" s="31"/>
       <c r="W2" s="2" t="s">
         <v>26</v>
       </c>
@@ -4477,12 +4477,12 @@
       <c r="Z4" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="AA4" s="23" t="s">
+      <c r="AA4" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="AB4" s="23"/>
-      <c r="AC4" s="23"/>
-      <c r="AD4" s="23"/>
+      <c r="AB4" s="32"/>
+      <c r="AC4" s="32"/>
+      <c r="AD4" s="32"/>
       <c r="AE4" s="7" t="s">
         <v>28</v>
       </c>
@@ -4531,11 +4531,11 @@
       <c r="P5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="V5" s="22" t="s">
+      <c r="V5" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="W5" s="22"/>
-      <c r="X5" s="22"/>
+      <c r="W5" s="31"/>
+      <c r="X5" s="31"/>
       <c r="Y5">
         <v>49</v>
       </c>
@@ -4556,18 +4556,18 @@
       <c r="AI5" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AJ5" s="21" t="s">
+      <c r="AJ5" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="AK5" s="21"/>
+      <c r="AK5" s="33"/>
       <c r="AL5" s="12" t="s">
         <v>81</v>
       </c>
       <c r="AM5" s="12"/>
-      <c r="AN5" s="21" t="s">
+      <c r="AN5" s="33" t="s">
         <v>82</v>
       </c>
-      <c r="AO5" s="21"/>
+      <c r="AO5" s="33"/>
       <c r="AP5" s="12" t="s">
         <v>83</v>
       </c>
@@ -4688,17 +4688,17 @@
       <c r="AI7" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="AJ7" s="22" t="s">
+      <c r="AJ7" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="AK7" s="22"/>
+      <c r="AK7" s="31"/>
       <c r="AL7">
         <v>1</v>
       </c>
-      <c r="AN7" s="22" t="s">
+      <c r="AN7" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="AO7" s="22"/>
+      <c r="AO7" s="31"/>
       <c r="AP7">
         <v>49</v>
       </c>
@@ -4742,12 +4742,12 @@
       <c r="R8" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="S8" s="22" t="s">
+      <c r="S8" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="T8" s="22"/>
-      <c r="U8" s="22"/>
-      <c r="V8" s="22"/>
+      <c r="T8" s="31"/>
+      <c r="U8" s="31"/>
+      <c r="V8" s="31"/>
       <c r="W8" s="2" t="s">
         <v>26</v>
       </c>
@@ -4755,18 +4755,18 @@
       <c r="AI8" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="AJ8" s="20" t="s">
+      <c r="AJ8" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="AK8" s="20"/>
+      <c r="AK8" s="34"/>
       <c r="AL8" s="18">
         <v>1</v>
       </c>
       <c r="AM8" s="18"/>
-      <c r="AN8" s="20" t="s">
+      <c r="AN8" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="AO8" s="20"/>
+      <c r="AO8" s="34"/>
       <c r="AP8" s="18">
         <v>49</v>
       </c>
@@ -4845,12 +4845,12 @@
       <c r="Z9" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="AA9" s="23" t="s">
+      <c r="AA9" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="AB9" s="23"/>
-      <c r="AC9" s="23"/>
-      <c r="AD9" s="23"/>
+      <c r="AB9" s="32"/>
+      <c r="AC9" s="32"/>
+      <c r="AD9" s="32"/>
       <c r="AE9" s="7" t="s">
         <v>28</v>
       </c>
@@ -4979,11 +4979,11 @@
       <c r="P11" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="V11" s="22" t="s">
+      <c r="V11" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="W11" s="22"/>
-      <c r="X11" s="22"/>
+      <c r="W11" s="31"/>
+      <c r="X11" s="31"/>
       <c r="Y11">
         <v>49</v>
       </c>
@@ -5003,18 +5003,18 @@
       <c r="AI11" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AJ11" s="21" t="s">
+      <c r="AJ11" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="AK11" s="21"/>
+      <c r="AK11" s="33"/>
       <c r="AL11" s="12" t="s">
         <v>81</v>
       </c>
       <c r="AM11" s="12"/>
-      <c r="AN11" s="21" t="s">
+      <c r="AN11" s="33" t="s">
         <v>82</v>
       </c>
-      <c r="AO11" s="21"/>
+      <c r="AO11" s="33"/>
       <c r="AP11" s="12" t="s">
         <v>83</v>
       </c>
@@ -5106,12 +5106,12 @@
       <c r="Z13" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="AA13" s="23" t="s">
+      <c r="AA13" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="AB13" s="23"/>
-      <c r="AC13" s="23"/>
-      <c r="AD13" s="23"/>
+      <c r="AB13" s="32"/>
+      <c r="AC13" s="32"/>
+      <c r="AD13" s="32"/>
       <c r="AE13" s="7" t="s">
         <v>28</v>
       </c>
@@ -5119,18 +5119,18 @@
       <c r="AI13" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="AJ13" s="20" t="s">
+      <c r="AJ13" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="AK13" s="20"/>
+      <c r="AK13" s="34"/>
       <c r="AL13" s="18">
         <v>1</v>
       </c>
       <c r="AM13" s="18"/>
-      <c r="AN13" s="20" t="s">
+      <c r="AN13" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="AO13" s="20"/>
+      <c r="AO13" s="34"/>
       <c r="AP13" s="18">
         <v>49</v>
       </c>
@@ -5190,12 +5190,12 @@
       <c r="R14" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="S14" s="22" t="s">
+      <c r="S14" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="T14" s="22"/>
-      <c r="U14" s="22"/>
-      <c r="V14" s="22"/>
+      <c r="T14" s="31"/>
+      <c r="U14" s="31"/>
+      <c r="V14" s="31"/>
       <c r="W14" s="2" t="s">
         <v>26</v>
       </c>
@@ -5215,10 +5215,10 @@
       <c r="AF14" s="2"/>
       <c r="AG14" s="2"/>
       <c r="AI14" s="2"/>
-      <c r="AJ14" s="22"/>
-      <c r="AK14" s="22"/>
-      <c r="AN14" s="22"/>
-      <c r="AO14" s="22"/>
+      <c r="AJ14" s="31"/>
+      <c r="AK14" s="31"/>
+      <c r="AN14" s="31"/>
+      <c r="AO14" s="31"/>
     </row>
     <row r="15" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B15">
@@ -5364,18 +5364,18 @@
       <c r="AI16" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AJ16" s="21" t="s">
+      <c r="AJ16" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="AK16" s="21"/>
+      <c r="AK16" s="33"/>
       <c r="AL16" s="12" t="s">
         <v>81</v>
       </c>
       <c r="AM16" s="12"/>
-      <c r="AN16" s="21" t="s">
+      <c r="AN16" s="33" t="s">
         <v>82</v>
       </c>
-      <c r="AO16" s="21"/>
+      <c r="AO16" s="33"/>
       <c r="AP16" s="12" t="s">
         <v>83</v>
       </c>
@@ -5430,11 +5430,11 @@
       <c r="P17" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="V17" s="22" t="s">
+      <c r="V17" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="W17" s="22"/>
-      <c r="X17" s="22"/>
+      <c r="W17" s="31"/>
+      <c r="X17" s="31"/>
       <c r="Y17">
         <v>49</v>
       </c>
@@ -5475,12 +5475,12 @@
       <c r="Z18" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="AA18" s="23" t="s">
+      <c r="AA18" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="AB18" s="23"/>
-      <c r="AC18" s="23"/>
-      <c r="AD18" s="23"/>
+      <c r="AB18" s="32"/>
+      <c r="AC18" s="32"/>
+      <c r="AD18" s="32"/>
       <c r="AE18" s="7" t="s">
         <v>28</v>
       </c>
@@ -5488,18 +5488,18 @@
       <c r="AI18" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="AJ18" s="20" t="s">
+      <c r="AJ18" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="AK18" s="20"/>
+      <c r="AK18" s="34"/>
       <c r="AL18" s="18">
         <v>1</v>
       </c>
       <c r="AM18" s="18"/>
-      <c r="AN18" s="20" t="s">
+      <c r="AN18" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="AO18" s="20"/>
+      <c r="AO18" s="34"/>
       <c r="AP18" s="18">
         <v>49</v>
       </c>
@@ -5617,12 +5617,12 @@
       <c r="R20" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="S20" s="22" t="s">
+      <c r="S20" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="T20" s="22"/>
-      <c r="U20" s="22"/>
-      <c r="V20" s="22"/>
+      <c r="T20" s="31"/>
+      <c r="U20" s="31"/>
+      <c r="V20" s="31"/>
       <c r="W20" s="2" t="s">
         <v>26</v>
       </c>
@@ -5643,18 +5643,18 @@
       <c r="AI20" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AJ20" s="21" t="s">
+      <c r="AJ20" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="AK20" s="21"/>
+      <c r="AK20" s="33"/>
       <c r="AL20" s="12" t="s">
         <v>81</v>
       </c>
       <c r="AM20" s="12"/>
-      <c r="AN20" s="21" t="s">
+      <c r="AN20" s="33" t="s">
         <v>82</v>
       </c>
-      <c r="AO20" s="21"/>
+      <c r="AO20" s="33"/>
       <c r="AP20" s="12" t="s">
         <v>83</v>
       </c>
@@ -5803,18 +5803,18 @@
       <c r="AI22" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="AJ22" s="20" t="s">
+      <c r="AJ22" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="AK22" s="20"/>
+      <c r="AK22" s="34"/>
       <c r="AL22" s="18">
         <v>2</v>
       </c>
       <c r="AM22" s="18"/>
-      <c r="AN22" s="20" t="s">
+      <c r="AN22" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="AO22" s="20"/>
+      <c r="AO22" s="34"/>
       <c r="AP22" s="18">
         <v>2</v>
       </c>
@@ -5855,11 +5855,11 @@
       <c r="I23">
         <v>21</v>
       </c>
-      <c r="V23" s="22" t="s">
+      <c r="V23" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="W23" s="22"/>
-      <c r="X23" s="22"/>
+      <c r="W23" s="31"/>
+      <c r="X23" s="31"/>
       <c r="Y23">
         <v>49</v>
       </c>
@@ -5910,18 +5910,18 @@
       <c r="AI24" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AJ24" s="21" t="s">
+      <c r="AJ24" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="AK24" s="21"/>
+      <c r="AK24" s="33"/>
       <c r="AL24" s="12" t="s">
         <v>81</v>
       </c>
       <c r="AM24" s="12"/>
-      <c r="AN24" s="21" t="s">
+      <c r="AN24" s="33" t="s">
         <v>82</v>
       </c>
-      <c r="AO24" s="21"/>
+      <c r="AO24" s="33"/>
       <c r="AP24" s="12" t="s">
         <v>83</v>
       </c>
@@ -6006,12 +6006,12 @@
       <c r="R26" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="S26" s="22" t="s">
+      <c r="S26" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="T26" s="22"/>
-      <c r="U26" s="22"/>
-      <c r="V26" s="22"/>
+      <c r="T26" s="31"/>
+      <c r="U26" s="31"/>
+      <c r="V26" s="31"/>
       <c r="W26" s="2" t="s">
         <v>28</v>
       </c>
@@ -6019,18 +6019,18 @@
       <c r="AI26" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="AJ26" s="20" t="s">
+      <c r="AJ26" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="AK26" s="20"/>
+      <c r="AK26" s="34"/>
       <c r="AL26" s="18">
         <v>2</v>
       </c>
       <c r="AM26" s="18"/>
-      <c r="AN26" s="20" t="s">
+      <c r="AN26" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="AO26" s="20"/>
+      <c r="AO26" s="34"/>
       <c r="AP26" s="18">
         <v>2</v>
       </c>
@@ -6200,29 +6200,29 @@
       <c r="P29" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="V29" s="22" t="s">
+      <c r="V29" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="W29" s="22"/>
-      <c r="X29" s="22"/>
+      <c r="W29" s="31"/>
+      <c r="X29" s="31"/>
       <c r="Y29" s="10">
         <v>2</v>
       </c>
       <c r="AI29" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AJ29" s="21" t="s">
+      <c r="AJ29" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="AK29" s="21"/>
+      <c r="AK29" s="33"/>
       <c r="AL29" s="12" t="s">
         <v>81</v>
       </c>
       <c r="AM29" s="12"/>
-      <c r="AN29" s="21" t="s">
+      <c r="AN29" s="33" t="s">
         <v>82</v>
       </c>
-      <c r="AO29" s="21"/>
+      <c r="AO29" s="33"/>
       <c r="AP29" s="12" t="s">
         <v>83</v>
       </c>
@@ -6330,17 +6330,17 @@
       <c r="AI31" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="AJ31" s="22" t="s">
+      <c r="AJ31" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="AK31" s="22"/>
+      <c r="AK31" s="31"/>
       <c r="AL31">
         <v>3</v>
       </c>
-      <c r="AN31" s="22" t="s">
+      <c r="AN31" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="AO31" s="22"/>
+      <c r="AO31" s="31"/>
       <c r="AP31">
         <v>4</v>
       </c>
@@ -6400,12 +6400,12 @@
       <c r="R32" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="S32" s="22" t="s">
+      <c r="S32" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="T32" s="22"/>
-      <c r="U32" s="22"/>
-      <c r="V32" s="22"/>
+      <c r="T32" s="31"/>
+      <c r="U32" s="31"/>
+      <c r="V32" s="31"/>
       <c r="W32" s="2" t="s">
         <v>28</v>
       </c>
@@ -6413,17 +6413,17 @@
       <c r="AI32" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="AJ32" s="22" t="s">
+      <c r="AJ32" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="AK32" s="22"/>
+      <c r="AK32" s="31"/>
       <c r="AL32">
         <v>3</v>
       </c>
-      <c r="AN32" s="22" t="s">
+      <c r="AN32" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="AO32" s="22"/>
+      <c r="AO32" s="31"/>
       <c r="AP32">
         <v>4</v>
       </c>
@@ -6486,17 +6486,17 @@
       <c r="AI33" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="AJ33" s="22" t="s">
+      <c r="AJ33" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="AK33" s="22"/>
+      <c r="AK33" s="31"/>
       <c r="AL33">
         <v>5</v>
       </c>
-      <c r="AN33" s="22" t="s">
+      <c r="AN33" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="AO33" s="22"/>
+      <c r="AO33" s="31"/>
       <c r="AP33">
         <v>6</v>
       </c>
@@ -6578,18 +6578,18 @@
       <c r="AI34" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="AJ34" s="20" t="s">
+      <c r="AJ34" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="AK34" s="20"/>
+      <c r="AK34" s="34"/>
       <c r="AL34" s="18">
         <v>5</v>
       </c>
       <c r="AM34" s="18"/>
-      <c r="AN34" s="20" t="s">
+      <c r="AN34" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="AO34" s="20"/>
+      <c r="AO34" s="34"/>
       <c r="AP34" s="18">
         <v>6</v>
       </c>
@@ -6646,11 +6646,11 @@
       <c r="P35" t="s">
         <v>29</v>
       </c>
-      <c r="V35" s="22" t="s">
+      <c r="V35" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="W35" s="22"/>
-      <c r="X35" s="22"/>
+      <c r="W35" s="31"/>
+      <c r="X35" s="31"/>
       <c r="Y35" s="10">
         <v>2</v>
       </c>
@@ -6719,18 +6719,18 @@
       <c r="AI37" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AJ37" s="21" t="s">
+      <c r="AJ37" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="AK37" s="21"/>
+      <c r="AK37" s="33"/>
       <c r="AL37" s="12" t="s">
         <v>81</v>
       </c>
       <c r="AM37" s="12"/>
-      <c r="AN37" s="21" t="s">
+      <c r="AN37" s="33" t="s">
         <v>82</v>
       </c>
-      <c r="AO37" s="21"/>
+      <c r="AO37" s="33"/>
       <c r="AP37" s="12" t="s">
         <v>83</v>
       </c>
@@ -6746,12 +6746,12 @@
       <c r="R38" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="S38" s="22" t="s">
+      <c r="S38" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="T38" s="22"/>
-      <c r="U38" s="22"/>
-      <c r="V38" s="22"/>
+      <c r="T38" s="31"/>
+      <c r="U38" s="31"/>
+      <c r="V38" s="31"/>
       <c r="W38" s="2" t="s">
         <v>29</v>
       </c>
@@ -6802,18 +6802,18 @@
       <c r="AI39" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="AJ39" s="20" t="s">
+      <c r="AJ39" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="AK39" s="20"/>
+      <c r="AK39" s="34"/>
       <c r="AL39" s="18">
         <v>3</v>
       </c>
       <c r="AM39" s="18"/>
-      <c r="AN39" s="20" t="s">
+      <c r="AN39" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="AO39" s="20"/>
+      <c r="AO39" s="34"/>
       <c r="AP39" s="18">
         <v>4</v>
       </c>
@@ -6924,29 +6924,29 @@
       <c r="P42" t="s">
         <v>43</v>
       </c>
-      <c r="V42" s="22" t="s">
+      <c r="V42" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="W42" s="22"/>
-      <c r="X42" s="22"/>
+      <c r="W42" s="31"/>
+      <c r="X42" s="31"/>
       <c r="Y42">
         <v>6</v>
       </c>
       <c r="AI42" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AJ42" s="21" t="s">
+      <c r="AJ42" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="AK42" s="21"/>
+      <c r="AK42" s="33"/>
       <c r="AL42" s="12" t="s">
         <v>81</v>
       </c>
       <c r="AM42" s="12"/>
-      <c r="AN42" s="21" t="s">
+      <c r="AN42" s="33" t="s">
         <v>82</v>
       </c>
-      <c r="AO42" s="21"/>
+      <c r="AO42" s="33"/>
       <c r="AP42" s="12" t="s">
         <v>83</v>
       </c>
@@ -6986,18 +6986,18 @@
       <c r="AI44" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="AJ44" s="20" t="s">
+      <c r="AJ44" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="AK44" s="20"/>
+      <c r="AK44" s="34"/>
       <c r="AL44" s="18">
         <v>3</v>
       </c>
       <c r="AM44" s="18"/>
-      <c r="AN44" s="20" t="s">
+      <c r="AN44" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="AO44" s="20"/>
+      <c r="AO44" s="34"/>
       <c r="AP44" s="18">
         <v>4</v>
       </c>
@@ -7031,12 +7031,12 @@
       <c r="R45" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="S45" s="22" t="s">
+      <c r="S45" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="T45" s="22"/>
-      <c r="U45" s="22"/>
-      <c r="V45" s="22"/>
+      <c r="T45" s="31"/>
+      <c r="U45" s="31"/>
+      <c r="V45" s="31"/>
       <c r="W45" s="2" t="s">
         <v>29</v>
       </c>
@@ -7081,18 +7081,18 @@
       <c r="AI46" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AJ46" s="21" t="s">
+      <c r="AJ46" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="AK46" s="21"/>
+      <c r="AK46" s="33"/>
       <c r="AL46" s="12" t="s">
         <v>81</v>
       </c>
       <c r="AM46" s="12"/>
-      <c r="AN46" s="21" t="s">
+      <c r="AN46" s="33" t="s">
         <v>82</v>
       </c>
-      <c r="AO46" s="21"/>
+      <c r="AO46" s="33"/>
       <c r="AP46" s="12" t="s">
         <v>83</v>
       </c>
@@ -7176,18 +7176,18 @@
       <c r="AI48" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="AJ48" s="20" t="s">
+      <c r="AJ48" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="AK48" s="20"/>
+      <c r="AK48" s="34"/>
       <c r="AL48" s="18">
         <v>5</v>
       </c>
       <c r="AM48" s="18"/>
-      <c r="AN48" s="20" t="s">
+      <c r="AN48" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="AO48" s="20"/>
+      <c r="AO48" s="34"/>
       <c r="AP48" s="18">
         <v>6</v>
       </c>
@@ -7218,11 +7218,11 @@
       <c r="P49" t="s">
         <v>43</v>
       </c>
-      <c r="V49" s="22" t="s">
+      <c r="V49" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="W49" s="22"/>
-      <c r="X49" s="22"/>
+      <c r="W49" s="31"/>
+      <c r="X49" s="31"/>
       <c r="Y49">
         <v>6</v>
       </c>
@@ -7283,12 +7283,12 @@
       <c r="R52" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="S52" s="22" t="s">
+      <c r="S52" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="T52" s="22"/>
-      <c r="U52" s="22"/>
-      <c r="V52" s="22"/>
+      <c r="T52" s="31"/>
+      <c r="U52" s="31"/>
+      <c r="V52" s="31"/>
       <c r="W52" s="2" t="s">
         <v>29</v>
       </c>
@@ -7412,11 +7412,11 @@
       <c r="P56" t="s">
         <v>43</v>
       </c>
-      <c r="V56" s="22" t="s">
+      <c r="V56" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="W56" s="22"/>
-      <c r="X56" s="22"/>
+      <c r="W56" s="31"/>
+      <c r="X56" s="31"/>
       <c r="Y56">
         <v>6</v>
       </c>
@@ -7459,12 +7459,12 @@
       <c r="R59" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="S59" s="22" t="s">
+      <c r="S59" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="T59" s="22"/>
-      <c r="U59" s="22"/>
-      <c r="V59" s="22"/>
+      <c r="T59" s="31"/>
+      <c r="U59" s="31"/>
+      <c r="V59" s="31"/>
       <c r="W59" s="2" t="s">
         <v>29</v>
       </c>
@@ -7587,11 +7587,11 @@
       <c r="Y62" s="10"/>
     </row>
     <row r="63" spans="12:25" x14ac:dyDescent="0.25">
-      <c r="V63" s="22" t="s">
+      <c r="V63" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="W63" s="22"/>
-      <c r="X63" s="22"/>
+      <c r="W63" s="31"/>
+      <c r="X63" s="31"/>
       <c r="Y63">
         <v>4</v>
       </c>
@@ -7958,23 +7958,43 @@
     </row>
   </sheetData>
   <mergeCells count="70">
-    <mergeCell ref="S2:V2"/>
-    <mergeCell ref="AA4:AD4"/>
-    <mergeCell ref="S38:V38"/>
-    <mergeCell ref="S8:V8"/>
-    <mergeCell ref="AA9:AD9"/>
-    <mergeCell ref="V29:X29"/>
-    <mergeCell ref="S14:V14"/>
-    <mergeCell ref="AA13:AD13"/>
-    <mergeCell ref="S20:V20"/>
-    <mergeCell ref="AA18:AD18"/>
-    <mergeCell ref="S59:V59"/>
-    <mergeCell ref="V35:X35"/>
-    <mergeCell ref="V42:X42"/>
-    <mergeCell ref="V49:X49"/>
-    <mergeCell ref="V56:X56"/>
-    <mergeCell ref="S45:V45"/>
-    <mergeCell ref="S52:V52"/>
+    <mergeCell ref="AJ44:AK44"/>
+    <mergeCell ref="AN44:AO44"/>
+    <mergeCell ref="AJ46:AK46"/>
+    <mergeCell ref="AN46:AO46"/>
+    <mergeCell ref="AJ48:AK48"/>
+    <mergeCell ref="AN48:AO48"/>
+    <mergeCell ref="AJ42:AK42"/>
+    <mergeCell ref="AN42:AO42"/>
+    <mergeCell ref="AJ34:AK34"/>
+    <mergeCell ref="AN34:AO34"/>
+    <mergeCell ref="AJ37:AK37"/>
+    <mergeCell ref="AN37:AO37"/>
+    <mergeCell ref="AJ39:AK39"/>
+    <mergeCell ref="AN39:AO39"/>
+    <mergeCell ref="AJ31:AK31"/>
+    <mergeCell ref="AN31:AO31"/>
+    <mergeCell ref="AJ32:AK32"/>
+    <mergeCell ref="AN32:AO32"/>
+    <mergeCell ref="AJ33:AK33"/>
+    <mergeCell ref="AN33:AO33"/>
+    <mergeCell ref="AJ24:AK24"/>
+    <mergeCell ref="AN24:AO24"/>
+    <mergeCell ref="AJ26:AK26"/>
+    <mergeCell ref="AN26:AO26"/>
+    <mergeCell ref="AJ29:AK29"/>
+    <mergeCell ref="AN29:AO29"/>
+    <mergeCell ref="AJ18:AK18"/>
+    <mergeCell ref="AN18:AO18"/>
+    <mergeCell ref="AJ20:AK20"/>
+    <mergeCell ref="AN20:AO20"/>
+    <mergeCell ref="AJ22:AK22"/>
+    <mergeCell ref="AN22:AO22"/>
+    <mergeCell ref="AN13:AO13"/>
+    <mergeCell ref="AJ14:AK14"/>
+    <mergeCell ref="AN14:AO14"/>
+    <mergeCell ref="AJ16:AK16"/>
+    <mergeCell ref="AN16:AO16"/>
     <mergeCell ref="V63:X63"/>
     <mergeCell ref="AJ5:AK5"/>
     <mergeCell ref="AN5:AO5"/>
@@ -7991,43 +8011,23 @@
     <mergeCell ref="V11:X11"/>
     <mergeCell ref="V17:X17"/>
     <mergeCell ref="V23:X23"/>
-    <mergeCell ref="AN13:AO13"/>
-    <mergeCell ref="AJ14:AK14"/>
-    <mergeCell ref="AN14:AO14"/>
-    <mergeCell ref="AJ16:AK16"/>
-    <mergeCell ref="AN16:AO16"/>
-    <mergeCell ref="AJ18:AK18"/>
-    <mergeCell ref="AN18:AO18"/>
-    <mergeCell ref="AJ20:AK20"/>
-    <mergeCell ref="AN20:AO20"/>
-    <mergeCell ref="AJ22:AK22"/>
-    <mergeCell ref="AN22:AO22"/>
-    <mergeCell ref="AJ24:AK24"/>
-    <mergeCell ref="AN24:AO24"/>
-    <mergeCell ref="AJ26:AK26"/>
-    <mergeCell ref="AN26:AO26"/>
-    <mergeCell ref="AJ29:AK29"/>
-    <mergeCell ref="AN29:AO29"/>
-    <mergeCell ref="AJ31:AK31"/>
-    <mergeCell ref="AN31:AO31"/>
-    <mergeCell ref="AJ32:AK32"/>
-    <mergeCell ref="AN32:AO32"/>
-    <mergeCell ref="AJ33:AK33"/>
-    <mergeCell ref="AN33:AO33"/>
-    <mergeCell ref="AJ42:AK42"/>
-    <mergeCell ref="AN42:AO42"/>
-    <mergeCell ref="AJ34:AK34"/>
-    <mergeCell ref="AN34:AO34"/>
-    <mergeCell ref="AJ37:AK37"/>
-    <mergeCell ref="AN37:AO37"/>
-    <mergeCell ref="AJ39:AK39"/>
-    <mergeCell ref="AN39:AO39"/>
-    <mergeCell ref="AJ44:AK44"/>
-    <mergeCell ref="AN44:AO44"/>
-    <mergeCell ref="AJ46:AK46"/>
-    <mergeCell ref="AN46:AO46"/>
-    <mergeCell ref="AJ48:AK48"/>
-    <mergeCell ref="AN48:AO48"/>
+    <mergeCell ref="S59:V59"/>
+    <mergeCell ref="V35:X35"/>
+    <mergeCell ref="V42:X42"/>
+    <mergeCell ref="V49:X49"/>
+    <mergeCell ref="V56:X56"/>
+    <mergeCell ref="S45:V45"/>
+    <mergeCell ref="S52:V52"/>
+    <mergeCell ref="S2:V2"/>
+    <mergeCell ref="AA4:AD4"/>
+    <mergeCell ref="S38:V38"/>
+    <mergeCell ref="S8:V8"/>
+    <mergeCell ref="AA9:AD9"/>
+    <mergeCell ref="V29:X29"/>
+    <mergeCell ref="S14:V14"/>
+    <mergeCell ref="AA13:AD13"/>
+    <mergeCell ref="S20:V20"/>
+    <mergeCell ref="AA18:AD18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8062,48 +8062,48 @@
       <c r="A7" t="s">
         <v>104</v>
       </c>
-      <c r="M7" s="27" t="s">
+      <c r="M7" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="O7" s="27" t="s">
+      <c r="O7" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="Q7" s="27" t="s">
+      <c r="Q7" s="23" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="E8" s="25" t="s">
+      <c r="E8" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="F8" s="25" t="s">
+      <c r="F8" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="24" t="s">
+      <c r="G8" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="H8" s="24" t="s">
+      <c r="H8" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="I8" s="24" t="s">
+      <c r="I8" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="M8" s="30" t="s">
+      <c r="M8" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="O8" s="30" t="s">
+      <c r="O8" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="Q8" s="30" t="s">
+      <c r="Q8" s="26" t="s">
         <v>117</v>
       </c>
     </row>
@@ -8126,19 +8126,19 @@
       <c r="G9" t="s">
         <v>101</v>
       </c>
-      <c r="H9" s="26">
+      <c r="H9" s="22">
         <v>46091</v>
       </c>
       <c r="I9" t="s">
         <v>102</v>
       </c>
-      <c r="M9" s="28" t="s">
+      <c r="M9" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="O9" s="28" t="s">
+      <c r="O9" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="Q9" s="28" t="s">
+      <c r="Q9" s="24" t="s">
         <v>113</v>
       </c>
     </row>
@@ -8161,40 +8161,40 @@
       <c r="G10" t="s">
         <v>101</v>
       </c>
-      <c r="H10" s="26">
+      <c r="H10" s="22">
         <v>46091</v>
       </c>
       <c r="I10" t="s">
         <v>102</v>
       </c>
-      <c r="M10" s="28" t="s">
+      <c r="M10" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="O10" s="29" t="s">
+      <c r="O10" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="Q10" s="28" t="s">
+      <c r="Q10" s="24" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M11" s="28" t="s">
+      <c r="M11" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="Q11" s="28" t="s">
+      <c r="Q11" s="24" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M12" s="28" t="s">
+      <c r="M12" s="24" t="s">
         <v>112</v>
       </c>
-      <c r="Q12" s="29" t="s">
+      <c r="Q12" s="25" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M13" s="29" t="s">
+      <c r="M13" s="25" t="s">
         <v>113</v>
       </c>
     </row>
@@ -8207,19 +8207,19 @@
       <c r="A17" t="s">
         <v>106</v>
       </c>
-      <c r="B17" s="28" t="s">
+      <c r="B17" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="C17" s="28" t="s">
+      <c r="C17" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="D17" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="E17" s="28" t="s">
+      <c r="E17" s="24" t="s">
         <v>112</v>
       </c>
-      <c r="F17" s="29" t="s">
+      <c r="F17" s="25" t="s">
         <v>113</v>
       </c>
     </row>
@@ -8395,13 +8395,13 @@
       <c r="A31" t="s">
         <v>122</v>
       </c>
-      <c r="B31" s="28" t="s">
+      <c r="B31" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="C31" s="28" t="s">
+      <c r="C31" s="24" t="s">
         <v>118</v>
       </c>
-      <c r="D31" s="28" t="s">
+      <c r="D31" s="24" t="s">
         <v>123</v>
       </c>
       <c r="E31" t="s">
@@ -8412,7 +8412,7 @@
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="33">
+      <c r="A32" s="29">
         <v>0</v>
       </c>
       <c r="B32" t="s">
@@ -8421,11 +8421,11 @@
       <c r="C32" t="s">
         <v>71</v>
       </c>
-      <c r="D32" s="32" t="s">
+      <c r="D32" s="28" t="s">
         <v>132</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H32" t="s">
         <v>128</v>
@@ -8444,11 +8444,11 @@
       <c r="C33" t="s">
         <v>59</v>
       </c>
-      <c r="D33" s="32" t="s">
+      <c r="D33" s="28" t="s">
         <v>130</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -8461,11 +8461,11 @@
       <c r="C34" t="s">
         <v>72</v>
       </c>
-      <c r="D34" s="32" t="s">
+      <c r="D34" s="28" t="s">
         <v>132</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -8478,15 +8478,15 @@
       <c r="C35" t="s">
         <v>63</v>
       </c>
-      <c r="D35" s="32" t="s">
+      <c r="D35" s="28" t="s">
         <v>130</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="33">
+      <c r="A36" s="29">
         <v>4</v>
       </c>
       <c r="B36" t="s">
@@ -8495,11 +8495,11 @@
       <c r="C36" t="s">
         <v>20</v>
       </c>
-      <c r="D36" s="32" t="s">
+      <c r="D36" s="28" t="s">
         <v>132</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -8512,11 +8512,11 @@
       <c r="C37" t="s">
         <v>61</v>
       </c>
-      <c r="D37" s="32" t="s">
+      <c r="D37" s="28" t="s">
         <v>130</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -8529,11 +8529,11 @@
       <c r="C38" t="s">
         <v>73</v>
       </c>
-      <c r="D38" s="32" t="s">
+      <c r="D38" s="28" t="s">
         <v>132</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -8546,15 +8546,15 @@
       <c r="C39" t="s">
         <v>65</v>
       </c>
-      <c r="D39" s="32" t="s">
+      <c r="D39" s="28" t="s">
         <v>130</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="34">
+      <c r="A40" s="30">
         <v>8</v>
       </c>
       <c r="B40" t="s">
@@ -8563,11 +8563,11 @@
       <c r="C40" t="s">
         <v>74</v>
       </c>
-      <c r="D40" s="32" t="s">
+      <c r="D40" s="28" t="s">
         <v>132</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -8580,11 +8580,16 @@
       <c r="C41" t="s">
         <v>76</v>
       </c>
-      <c r="D41" s="32" t="s">
+      <c r="D41" s="28" t="s">
         <v>130</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E42">
+        <v>-1</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -8597,11 +8602,11 @@
       <c r="C43" t="s">
         <v>71</v>
       </c>
-      <c r="D43" s="32" t="s">
+      <c r="D43" s="28" t="s">
         <v>132</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -8614,11 +8619,11 @@
       <c r="C44" t="s">
         <v>59</v>
       </c>
-      <c r="D44" s="32" t="s">
+      <c r="D44" s="28" t="s">
         <v>130</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -8631,11 +8636,11 @@
       <c r="C45" t="s">
         <v>72</v>
       </c>
-      <c r="D45" s="32" t="s">
+      <c r="D45" s="28" t="s">
         <v>132</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -8648,11 +8653,11 @@
       <c r="C46" t="s">
         <v>63</v>
       </c>
-      <c r="D46" s="32" t="s">
+      <c r="D46" s="28" t="s">
         <v>130</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -8665,11 +8670,11 @@
       <c r="C47" t="s">
         <v>20</v>
       </c>
-      <c r="D47" s="32" t="s">
+      <c r="D47" s="28" t="s">
         <v>132</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -8682,11 +8687,11 @@
       <c r="C48" t="s">
         <v>61</v>
       </c>
-      <c r="D48" s="32" t="s">
+      <c r="D48" s="28" t="s">
         <v>130</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -8699,11 +8704,11 @@
       <c r="C49" t="s">
         <v>73</v>
       </c>
-      <c r="D49" s="32" t="s">
+      <c r="D49" s="28" t="s">
         <v>132</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -8716,11 +8721,11 @@
       <c r="C50" t="s">
         <v>65</v>
       </c>
-      <c r="D50" s="32" t="s">
+      <c r="D50" s="28" t="s">
         <v>130</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -8733,11 +8738,11 @@
       <c r="C51" t="s">
         <v>74</v>
       </c>
-      <c r="D51" s="32" t="s">
+      <c r="D51" s="28" t="s">
         <v>132</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -8750,11 +8755,11 @@
       <c r="C52" t="s">
         <v>76</v>
       </c>
-      <c r="D52" s="32" t="s">
+      <c r="D52" s="28" t="s">
         <v>130</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
@@ -8789,13 +8794,13 @@
       <c r="A3" t="s">
         <v>122</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="24" t="s">
         <v>118</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="D3" s="24" t="s">
         <v>123</v>
       </c>
       <c r="E3" t="s">
@@ -8818,38 +8823,38 @@
       <c r="E4">
         <v>0</v>
       </c>
-      <c r="J4" s="27" t="s">
+      <c r="J4" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="L4" s="27" t="s">
+      <c r="L4" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="N4" s="27" t="s">
+      <c r="N4" s="23" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J5" s="30" t="s">
+      <c r="J5" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="L5" s="30" t="s">
+      <c r="L5" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="N5" s="30" t="s">
+      <c r="N5" s="26" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D6" s="31" t="s">
+      <c r="D6" s="27" t="s">
         <v>124</v>
       </c>
-      <c r="J6" s="28" t="s">
+      <c r="J6" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="L6" s="28" t="s">
+      <c r="L6" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="N6" s="28" t="s">
+      <c r="N6" s="24" t="s">
         <v>113</v>
       </c>
     </row>
@@ -8869,32 +8874,32 @@
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="J7" s="28" t="s">
+      <c r="J7" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="L7" s="29" t="s">
+      <c r="L7" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="N7" s="28" t="s">
+      <c r="N7" s="24" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J8" s="28" t="s">
+      <c r="J8" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="N8" s="28" t="s">
+      <c r="N8" s="24" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D9" s="31" t="s">
+      <c r="D9" s="27" t="s">
         <v>124</v>
       </c>
-      <c r="J9" s="28" t="s">
+      <c r="J9" s="24" t="s">
         <v>112</v>
       </c>
-      <c r="N9" s="29" t="s">
+      <c r="N9" s="25" t="s">
         <v>120</v>
       </c>
     </row>
@@ -8914,12 +8919,12 @@
       <c r="E10">
         <v>0</v>
       </c>
-      <c r="J10" s="29" t="s">
+      <c r="J10" s="25" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D12" s="31" t="s">
+      <c r="D12" s="27" t="s">
         <v>124</v>
       </c>
     </row>
@@ -8941,7 +8946,7 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D15" s="31" t="s">
+      <c r="D15" s="27" t="s">
         <v>124</v>
       </c>
     </row>
@@ -8963,7 +8968,7 @@
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D18" s="31" t="s">
+      <c r="D18" s="27" t="s">
         <v>124</v>
       </c>
     </row>
@@ -8985,7 +8990,7 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D21" s="31" t="s">
+      <c r="D21" s="27" t="s">
         <v>124</v>
       </c>
     </row>
@@ -9007,7 +9012,7 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D24" s="31" t="s">
+      <c r="D24" s="27" t="s">
         <v>124</v>
       </c>
     </row>
@@ -9029,7 +9034,7 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D27" s="31" t="s">
+      <c r="D27" s="27" t="s">
         <v>124</v>
       </c>
     </row>
@@ -9051,7 +9056,7 @@
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D30" s="31" t="s">
+      <c r="D30" s="27" t="s">
         <v>124</v>
       </c>
     </row>
@@ -9073,7 +9078,7 @@
       </c>
     </row>
     <row r="33" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D33" s="31" t="s">
+      <c r="D33" s="27" t="s">
         <v>124</v>
       </c>
     </row>

--- a/VPD PO download generator/trying stuff business systems.xlsx
+++ b/VPD PO download generator/trying stuff business systems.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwa25\source\repos\VPD PO download generator\VPD PO download generator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8ECCF37-B949-422D-BFEE-FD37EBD693C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D4E2C95-C771-4C9A-8CE7-0FC2421EDA7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{D51960FC-1269-4ACE-8C84-C0CBF6215B21}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{D51960FC-1269-4ACE-8C84-C0CBF6215B21}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="1st attempt optimization, part2" sheetId="3" r:id="rId3"/>
     <sheet name="Sheet2" sheetId="4" r:id="rId4"/>
     <sheet name="orderLists" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet2 (2)" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1242" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="139">
   <si>
     <t>KSO5088990 PVPDFJB    TWHWHNA01AA001CR-SO-5088990-1-1                                            L07975</t>
   </si>
@@ -428,6 +429,24 @@
   </si>
   <si>
     <t>3, [ ]</t>
+  </si>
+  <si>
+    <t>[ ]</t>
+  </si>
+  <si>
+    <t>3,4</t>
+  </si>
+  <si>
+    <t>6,7</t>
+  </si>
+  <si>
+    <t>5,6</t>
+  </si>
+  <si>
+    <t>5,5</t>
+  </si>
+  <si>
+    <t>7,7</t>
   </si>
 </sst>
 </file>
@@ -481,7 +500,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -548,8 +567,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -674,11 +699,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -720,12 +782,42 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4210,12 +4302,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="AA23:AD23"/>
-    <mergeCell ref="AA27:AD27"/>
-    <mergeCell ref="AA4:AD4"/>
-    <mergeCell ref="AA9:AD9"/>
-    <mergeCell ref="AA13:AD13"/>
-    <mergeCell ref="AA18:AD18"/>
     <mergeCell ref="S4:V4"/>
     <mergeCell ref="S9:V9"/>
     <mergeCell ref="S13:V13"/>
@@ -4224,6 +4310,12 @@
     <mergeCell ref="AI4:AL4"/>
     <mergeCell ref="AI9:AL9"/>
     <mergeCell ref="AI15:AL15"/>
+    <mergeCell ref="AA23:AD23"/>
+    <mergeCell ref="AA27:AD27"/>
+    <mergeCell ref="AA4:AD4"/>
+    <mergeCell ref="AA9:AD9"/>
+    <mergeCell ref="AA13:AD13"/>
+    <mergeCell ref="AA18:AD18"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4556,18 +4648,18 @@
       <c r="AI5" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AJ5" s="33" t="s">
+      <c r="AJ5" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="AK5" s="33"/>
+      <c r="AK5" s="34"/>
       <c r="AL5" s="12" t="s">
         <v>81</v>
       </c>
       <c r="AM5" s="12"/>
-      <c r="AN5" s="33" t="s">
+      <c r="AN5" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="AO5" s="33"/>
+      <c r="AO5" s="34"/>
       <c r="AP5" s="12" t="s">
         <v>83</v>
       </c>
@@ -4755,18 +4847,18 @@
       <c r="AI8" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="AJ8" s="34" t="s">
+      <c r="AJ8" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="AK8" s="34"/>
+      <c r="AK8" s="33"/>
       <c r="AL8" s="18">
         <v>1</v>
       </c>
       <c r="AM8" s="18"/>
-      <c r="AN8" s="34" t="s">
+      <c r="AN8" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="AO8" s="34"/>
+      <c r="AO8" s="33"/>
       <c r="AP8" s="18">
         <v>49</v>
       </c>
@@ -5003,18 +5095,18 @@
       <c r="AI11" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AJ11" s="33" t="s">
+      <c r="AJ11" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="AK11" s="33"/>
+      <c r="AK11" s="34"/>
       <c r="AL11" s="12" t="s">
         <v>81</v>
       </c>
       <c r="AM11" s="12"/>
-      <c r="AN11" s="33" t="s">
+      <c r="AN11" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="AO11" s="33"/>
+      <c r="AO11" s="34"/>
       <c r="AP11" s="12" t="s">
         <v>83</v>
       </c>
@@ -5119,18 +5211,18 @@
       <c r="AI13" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="AJ13" s="34" t="s">
+      <c r="AJ13" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="AK13" s="34"/>
+      <c r="AK13" s="33"/>
       <c r="AL13" s="18">
         <v>1</v>
       </c>
       <c r="AM13" s="18"/>
-      <c r="AN13" s="34" t="s">
+      <c r="AN13" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="AO13" s="34"/>
+      <c r="AO13" s="33"/>
       <c r="AP13" s="18">
         <v>49</v>
       </c>
@@ -5364,18 +5456,18 @@
       <c r="AI16" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AJ16" s="33" t="s">
+      <c r="AJ16" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="AK16" s="33"/>
+      <c r="AK16" s="34"/>
       <c r="AL16" s="12" t="s">
         <v>81</v>
       </c>
       <c r="AM16" s="12"/>
-      <c r="AN16" s="33" t="s">
+      <c r="AN16" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="AO16" s="33"/>
+      <c r="AO16" s="34"/>
       <c r="AP16" s="12" t="s">
         <v>83</v>
       </c>
@@ -5488,18 +5580,18 @@
       <c r="AI18" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="AJ18" s="34" t="s">
+      <c r="AJ18" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="AK18" s="34"/>
+      <c r="AK18" s="33"/>
       <c r="AL18" s="18">
         <v>1</v>
       </c>
       <c r="AM18" s="18"/>
-      <c r="AN18" s="34" t="s">
+      <c r="AN18" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="AO18" s="34"/>
+      <c r="AO18" s="33"/>
       <c r="AP18" s="18">
         <v>49</v>
       </c>
@@ -5643,18 +5735,18 @@
       <c r="AI20" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AJ20" s="33" t="s">
+      <c r="AJ20" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="AK20" s="33"/>
+      <c r="AK20" s="34"/>
       <c r="AL20" s="12" t="s">
         <v>81</v>
       </c>
       <c r="AM20" s="12"/>
-      <c r="AN20" s="33" t="s">
+      <c r="AN20" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="AO20" s="33"/>
+      <c r="AO20" s="34"/>
       <c r="AP20" s="12" t="s">
         <v>83</v>
       </c>
@@ -5803,18 +5895,18 @@
       <c r="AI22" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="AJ22" s="34" t="s">
+      <c r="AJ22" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="AK22" s="34"/>
+      <c r="AK22" s="33"/>
       <c r="AL22" s="18">
         <v>2</v>
       </c>
       <c r="AM22" s="18"/>
-      <c r="AN22" s="34" t="s">
+      <c r="AN22" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="AO22" s="34"/>
+      <c r="AO22" s="33"/>
       <c r="AP22" s="18">
         <v>2</v>
       </c>
@@ -5910,18 +6002,18 @@
       <c r="AI24" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AJ24" s="33" t="s">
+      <c r="AJ24" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="AK24" s="33"/>
+      <c r="AK24" s="34"/>
       <c r="AL24" s="12" t="s">
         <v>81</v>
       </c>
       <c r="AM24" s="12"/>
-      <c r="AN24" s="33" t="s">
+      <c r="AN24" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="AO24" s="33"/>
+      <c r="AO24" s="34"/>
       <c r="AP24" s="12" t="s">
         <v>83</v>
       </c>
@@ -6019,18 +6111,18 @@
       <c r="AI26" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="AJ26" s="34" t="s">
+      <c r="AJ26" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="AK26" s="34"/>
+      <c r="AK26" s="33"/>
       <c r="AL26" s="18">
         <v>2</v>
       </c>
       <c r="AM26" s="18"/>
-      <c r="AN26" s="34" t="s">
+      <c r="AN26" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="AO26" s="34"/>
+      <c r="AO26" s="33"/>
       <c r="AP26" s="18">
         <v>2</v>
       </c>
@@ -6211,18 +6303,18 @@
       <c r="AI29" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AJ29" s="33" t="s">
+      <c r="AJ29" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="AK29" s="33"/>
+      <c r="AK29" s="34"/>
       <c r="AL29" s="12" t="s">
         <v>81</v>
       </c>
       <c r="AM29" s="12"/>
-      <c r="AN29" s="33" t="s">
+      <c r="AN29" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="AO29" s="33"/>
+      <c r="AO29" s="34"/>
       <c r="AP29" s="12" t="s">
         <v>83</v>
       </c>
@@ -6578,18 +6670,18 @@
       <c r="AI34" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="AJ34" s="34" t="s">
+      <c r="AJ34" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="AK34" s="34"/>
+      <c r="AK34" s="33"/>
       <c r="AL34" s="18">
         <v>5</v>
       </c>
       <c r="AM34" s="18"/>
-      <c r="AN34" s="34" t="s">
+      <c r="AN34" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="AO34" s="34"/>
+      <c r="AO34" s="33"/>
       <c r="AP34" s="18">
         <v>6</v>
       </c>
@@ -6719,18 +6811,18 @@
       <c r="AI37" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AJ37" s="33" t="s">
+      <c r="AJ37" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="AK37" s="33"/>
+      <c r="AK37" s="34"/>
       <c r="AL37" s="12" t="s">
         <v>81</v>
       </c>
       <c r="AM37" s="12"/>
-      <c r="AN37" s="33" t="s">
+      <c r="AN37" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="AO37" s="33"/>
+      <c r="AO37" s="34"/>
       <c r="AP37" s="12" t="s">
         <v>83</v>
       </c>
@@ -6802,18 +6894,18 @@
       <c r="AI39" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="AJ39" s="34" t="s">
+      <c r="AJ39" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="AK39" s="34"/>
+      <c r="AK39" s="33"/>
       <c r="AL39" s="18">
         <v>3</v>
       </c>
       <c r="AM39" s="18"/>
-      <c r="AN39" s="34" t="s">
+      <c r="AN39" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="AO39" s="34"/>
+      <c r="AO39" s="33"/>
       <c r="AP39" s="18">
         <v>4</v>
       </c>
@@ -6935,18 +7027,18 @@
       <c r="AI42" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AJ42" s="33" t="s">
+      <c r="AJ42" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="AK42" s="33"/>
+      <c r="AK42" s="34"/>
       <c r="AL42" s="12" t="s">
         <v>81</v>
       </c>
       <c r="AM42" s="12"/>
-      <c r="AN42" s="33" t="s">
+      <c r="AN42" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="AO42" s="33"/>
+      <c r="AO42" s="34"/>
       <c r="AP42" s="12" t="s">
         <v>83</v>
       </c>
@@ -6986,18 +7078,18 @@
       <c r="AI44" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="AJ44" s="34" t="s">
+      <c r="AJ44" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="AK44" s="34"/>
+      <c r="AK44" s="33"/>
       <c r="AL44" s="18">
         <v>3</v>
       </c>
       <c r="AM44" s="18"/>
-      <c r="AN44" s="34" t="s">
+      <c r="AN44" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="AO44" s="34"/>
+      <c r="AO44" s="33"/>
       <c r="AP44" s="18">
         <v>4</v>
       </c>
@@ -7081,18 +7173,18 @@
       <c r="AI46" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AJ46" s="33" t="s">
+      <c r="AJ46" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="AK46" s="33"/>
+      <c r="AK46" s="34"/>
       <c r="AL46" s="12" t="s">
         <v>81</v>
       </c>
       <c r="AM46" s="12"/>
-      <c r="AN46" s="33" t="s">
+      <c r="AN46" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="AO46" s="33"/>
+      <c r="AO46" s="34"/>
       <c r="AP46" s="12" t="s">
         <v>83</v>
       </c>
@@ -7176,18 +7268,18 @@
       <c r="AI48" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="AJ48" s="34" t="s">
+      <c r="AJ48" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="AK48" s="34"/>
+      <c r="AK48" s="33"/>
       <c r="AL48" s="18">
         <v>5</v>
       </c>
       <c r="AM48" s="18"/>
-      <c r="AN48" s="34" t="s">
+      <c r="AN48" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="AO48" s="34"/>
+      <c r="AO48" s="33"/>
       <c r="AP48" s="18">
         <v>6</v>
       </c>
@@ -7958,43 +8050,23 @@
     </row>
   </sheetData>
   <mergeCells count="70">
-    <mergeCell ref="AJ44:AK44"/>
-    <mergeCell ref="AN44:AO44"/>
-    <mergeCell ref="AJ46:AK46"/>
-    <mergeCell ref="AN46:AO46"/>
-    <mergeCell ref="AJ48:AK48"/>
-    <mergeCell ref="AN48:AO48"/>
-    <mergeCell ref="AJ42:AK42"/>
-    <mergeCell ref="AN42:AO42"/>
-    <mergeCell ref="AJ34:AK34"/>
-    <mergeCell ref="AN34:AO34"/>
-    <mergeCell ref="AJ37:AK37"/>
-    <mergeCell ref="AN37:AO37"/>
-    <mergeCell ref="AJ39:AK39"/>
-    <mergeCell ref="AN39:AO39"/>
-    <mergeCell ref="AJ31:AK31"/>
-    <mergeCell ref="AN31:AO31"/>
-    <mergeCell ref="AJ32:AK32"/>
-    <mergeCell ref="AN32:AO32"/>
-    <mergeCell ref="AJ33:AK33"/>
-    <mergeCell ref="AN33:AO33"/>
-    <mergeCell ref="AJ24:AK24"/>
-    <mergeCell ref="AN24:AO24"/>
-    <mergeCell ref="AJ26:AK26"/>
-    <mergeCell ref="AN26:AO26"/>
-    <mergeCell ref="AJ29:AK29"/>
-    <mergeCell ref="AN29:AO29"/>
-    <mergeCell ref="AJ18:AK18"/>
-    <mergeCell ref="AN18:AO18"/>
-    <mergeCell ref="AJ20:AK20"/>
-    <mergeCell ref="AN20:AO20"/>
-    <mergeCell ref="AJ22:AK22"/>
-    <mergeCell ref="AN22:AO22"/>
-    <mergeCell ref="AN13:AO13"/>
-    <mergeCell ref="AJ14:AK14"/>
-    <mergeCell ref="AN14:AO14"/>
-    <mergeCell ref="AJ16:AK16"/>
-    <mergeCell ref="AN16:AO16"/>
+    <mergeCell ref="S2:V2"/>
+    <mergeCell ref="AA4:AD4"/>
+    <mergeCell ref="S38:V38"/>
+    <mergeCell ref="S8:V8"/>
+    <mergeCell ref="AA9:AD9"/>
+    <mergeCell ref="V29:X29"/>
+    <mergeCell ref="S14:V14"/>
+    <mergeCell ref="AA13:AD13"/>
+    <mergeCell ref="S20:V20"/>
+    <mergeCell ref="AA18:AD18"/>
+    <mergeCell ref="S59:V59"/>
+    <mergeCell ref="V35:X35"/>
+    <mergeCell ref="V42:X42"/>
+    <mergeCell ref="V49:X49"/>
+    <mergeCell ref="V56:X56"/>
+    <mergeCell ref="S45:V45"/>
+    <mergeCell ref="S52:V52"/>
     <mergeCell ref="V63:X63"/>
     <mergeCell ref="AJ5:AK5"/>
     <mergeCell ref="AN5:AO5"/>
@@ -8011,23 +8083,43 @@
     <mergeCell ref="V11:X11"/>
     <mergeCell ref="V17:X17"/>
     <mergeCell ref="V23:X23"/>
-    <mergeCell ref="S59:V59"/>
-    <mergeCell ref="V35:X35"/>
-    <mergeCell ref="V42:X42"/>
-    <mergeCell ref="V49:X49"/>
-    <mergeCell ref="V56:X56"/>
-    <mergeCell ref="S45:V45"/>
-    <mergeCell ref="S52:V52"/>
-    <mergeCell ref="S2:V2"/>
-    <mergeCell ref="AA4:AD4"/>
-    <mergeCell ref="S38:V38"/>
-    <mergeCell ref="S8:V8"/>
-    <mergeCell ref="AA9:AD9"/>
-    <mergeCell ref="V29:X29"/>
-    <mergeCell ref="S14:V14"/>
-    <mergeCell ref="AA13:AD13"/>
-    <mergeCell ref="S20:V20"/>
-    <mergeCell ref="AA18:AD18"/>
+    <mergeCell ref="AN13:AO13"/>
+    <mergeCell ref="AJ14:AK14"/>
+    <mergeCell ref="AN14:AO14"/>
+    <mergeCell ref="AJ16:AK16"/>
+    <mergeCell ref="AN16:AO16"/>
+    <mergeCell ref="AJ18:AK18"/>
+    <mergeCell ref="AN18:AO18"/>
+    <mergeCell ref="AJ20:AK20"/>
+    <mergeCell ref="AN20:AO20"/>
+    <mergeCell ref="AJ22:AK22"/>
+    <mergeCell ref="AN22:AO22"/>
+    <mergeCell ref="AJ24:AK24"/>
+    <mergeCell ref="AN24:AO24"/>
+    <mergeCell ref="AJ26:AK26"/>
+    <mergeCell ref="AN26:AO26"/>
+    <mergeCell ref="AJ29:AK29"/>
+    <mergeCell ref="AN29:AO29"/>
+    <mergeCell ref="AJ31:AK31"/>
+    <mergeCell ref="AN31:AO31"/>
+    <mergeCell ref="AJ32:AK32"/>
+    <mergeCell ref="AN32:AO32"/>
+    <mergeCell ref="AJ33:AK33"/>
+    <mergeCell ref="AN33:AO33"/>
+    <mergeCell ref="AJ42:AK42"/>
+    <mergeCell ref="AN42:AO42"/>
+    <mergeCell ref="AJ34:AK34"/>
+    <mergeCell ref="AN34:AO34"/>
+    <mergeCell ref="AJ37:AK37"/>
+    <mergeCell ref="AN37:AO37"/>
+    <mergeCell ref="AJ39:AK39"/>
+    <mergeCell ref="AN39:AO39"/>
+    <mergeCell ref="AJ44:AK44"/>
+    <mergeCell ref="AN44:AO44"/>
+    <mergeCell ref="AJ46:AK46"/>
+    <mergeCell ref="AN46:AO46"/>
+    <mergeCell ref="AJ48:AK48"/>
+    <mergeCell ref="AN48:AO48"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8587,11 +8679,6 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E42">
-        <v>-1</v>
-      </c>
-    </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>11</v>
@@ -8623,7 +8710,7 @@
         <v>130</v>
       </c>
       <c r="E44">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -8657,7 +8744,7 @@
         <v>130</v>
       </c>
       <c r="E46">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -8691,7 +8778,7 @@
         <v>130</v>
       </c>
       <c r="E48">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -8725,7 +8812,7 @@
         <v>130</v>
       </c>
       <c r="E50">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -8742,7 +8829,7 @@
         <v>132</v>
       </c>
       <c r="E51">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -8759,7 +8846,7 @@
         <v>130</v>
       </c>
       <c r="E52">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -9085,4 +9172,806 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAA950F9-476E-45D0-B1BB-4CA166267AA1}">
+  <dimension ref="A3:Q60"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" customWidth="1"/>
+    <col min="2" max="2" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23" customWidth="1"/>
+    <col min="14" max="14" width="1.5703125" customWidth="1"/>
+    <col min="15" max="15" width="18.140625" customWidth="1"/>
+    <col min="16" max="16" width="1.42578125" customWidth="1"/>
+    <col min="17" max="17" width="45.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>104</v>
+      </c>
+      <c r="M7" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="O7" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q7" s="23" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="H8" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="I8" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="M8" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="O8" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q8" s="26" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" t="s">
+        <v>99</v>
+      </c>
+      <c r="D9">
+        <v>71.5</v>
+      </c>
+      <c r="E9">
+        <v>95.5</v>
+      </c>
+      <c r="F9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G9" t="s">
+        <v>101</v>
+      </c>
+      <c r="H9" s="22">
+        <v>46091</v>
+      </c>
+      <c r="I9" t="s">
+        <v>102</v>
+      </c>
+      <c r="M9" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="O9" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q9" s="24" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" t="s">
+        <v>99</v>
+      </c>
+      <c r="D10">
+        <v>71.5</v>
+      </c>
+      <c r="E10">
+        <v>95.5</v>
+      </c>
+      <c r="F10" t="s">
+        <v>100</v>
+      </c>
+      <c r="G10" t="s">
+        <v>101</v>
+      </c>
+      <c r="H10" s="22">
+        <v>46091</v>
+      </c>
+      <c r="I10" t="s">
+        <v>102</v>
+      </c>
+      <c r="M10" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="O10" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q10" s="24" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M11" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q11" s="24" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M12" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q12" s="25" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M13" s="25" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>106</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="E17" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="F17" s="25" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>0</v>
+      </c>
+      <c r="B18" t="s">
+        <v>98</v>
+      </c>
+      <c r="C18" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18">
+        <v>35.561999999999998</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>1</v>
+      </c>
+      <c r="B19" t="s">
+        <v>98</v>
+      </c>
+      <c r="C19" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19">
+        <v>92.875</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>2</v>
+      </c>
+      <c r="B20" t="s">
+        <v>98</v>
+      </c>
+      <c r="C20" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20">
+        <v>35.561999999999998</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>3</v>
+      </c>
+      <c r="B21" t="s">
+        <v>98</v>
+      </c>
+      <c r="C21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21">
+        <v>92.875</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
+        <v>103</v>
+      </c>
+      <c r="C22" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22">
+        <v>35.561999999999998</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>5</v>
+      </c>
+      <c r="B23" t="s">
+        <v>103</v>
+      </c>
+      <c r="C23" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23">
+        <v>92.875</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>6</v>
+      </c>
+      <c r="B24" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24" t="s">
+        <v>45</v>
+      </c>
+      <c r="D24">
+        <v>35.561999999999998</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>7</v>
+      </c>
+      <c r="B25" t="s">
+        <v>103</v>
+      </c>
+      <c r="C25" t="s">
+        <v>46</v>
+      </c>
+      <c r="D25">
+        <v>92.875</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>121</v>
+      </c>
+      <c r="D30" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>122</v>
+      </c>
+      <c r="B31" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="C31" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="D31" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="E31" t="s">
+        <v>120</v>
+      </c>
+      <c r="H31" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="29">
+        <v>0</v>
+      </c>
+      <c r="B32" t="s">
+        <v>100</v>
+      </c>
+      <c r="C32" t="s">
+        <v>71</v>
+      </c>
+      <c r="D32" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="E32">
+        <v>-1</v>
+      </c>
+      <c r="H32" t="s">
+        <v>128</v>
+      </c>
+      <c r="I32" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>1</v>
+      </c>
+      <c r="B33" t="s">
+        <v>100</v>
+      </c>
+      <c r="C33" t="s">
+        <v>59</v>
+      </c>
+      <c r="D33" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="E33">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>2</v>
+      </c>
+      <c r="B34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C34" t="s">
+        <v>72</v>
+      </c>
+      <c r="D34" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="E34">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>3</v>
+      </c>
+      <c r="B35" t="s">
+        <v>100</v>
+      </c>
+      <c r="C35" t="s">
+        <v>63</v>
+      </c>
+      <c r="D35" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="E35">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="29">
+        <v>4</v>
+      </c>
+      <c r="B36" t="s">
+        <v>100</v>
+      </c>
+      <c r="C36" t="s">
+        <v>20</v>
+      </c>
+      <c r="D36" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="E36">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>5</v>
+      </c>
+      <c r="B37" t="s">
+        <v>100</v>
+      </c>
+      <c r="C37" t="s">
+        <v>61</v>
+      </c>
+      <c r="D37" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="E37">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>6</v>
+      </c>
+      <c r="B38" t="s">
+        <v>100</v>
+      </c>
+      <c r="C38" t="s">
+        <v>73</v>
+      </c>
+      <c r="D38" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="E38">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>7</v>
+      </c>
+      <c r="B39" t="s">
+        <v>100</v>
+      </c>
+      <c r="C39" t="s">
+        <v>65</v>
+      </c>
+      <c r="D39" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="E39">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="30">
+        <v>8</v>
+      </c>
+      <c r="B40" t="s">
+        <v>100</v>
+      </c>
+      <c r="C40" t="s">
+        <v>74</v>
+      </c>
+      <c r="D40" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="E40">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>9</v>
+      </c>
+      <c r="B41" t="s">
+        <v>100</v>
+      </c>
+      <c r="C41" t="s">
+        <v>76</v>
+      </c>
+      <c r="D41" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="E41">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="45">
+        <v>11</v>
+      </c>
+      <c r="B43" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="C43" s="46" t="s">
+        <v>71</v>
+      </c>
+      <c r="D43" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="E43" s="48">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="39">
+        <v>12</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D44" s="40" t="s">
+        <v>130</v>
+      </c>
+      <c r="E44" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="14"/>
+      <c r="B45" s="41"/>
+      <c r="C45" s="41"/>
+      <c r="D45" s="42" t="s">
+        <v>134</v>
+      </c>
+      <c r="E45" s="15"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="43"/>
+      <c r="B46" s="18"/>
+      <c r="C46" s="18"/>
+      <c r="D46" s="44" t="s">
+        <v>135</v>
+      </c>
+      <c r="E46" s="19"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="45">
+        <v>13</v>
+      </c>
+      <c r="B47" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="C47" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="D47" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="E47" s="48">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="39">
+        <v>14</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D48" s="40" t="s">
+        <v>130</v>
+      </c>
+      <c r="E48" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="14"/>
+      <c r="B49" s="41"/>
+      <c r="C49" s="41"/>
+      <c r="D49" s="42" t="s">
+        <v>134</v>
+      </c>
+      <c r="E49" s="15"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="43"/>
+      <c r="B50" s="18"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="44" t="s">
+        <v>136</v>
+      </c>
+      <c r="E50" s="19"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="45">
+        <v>15</v>
+      </c>
+      <c r="B51" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="C51" s="46" t="s">
+        <v>20</v>
+      </c>
+      <c r="D51" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="E51" s="48">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="39">
+        <v>16</v>
+      </c>
+      <c r="B52" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D52" s="40" t="s">
+        <v>130</v>
+      </c>
+      <c r="E52" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="14"/>
+      <c r="B53" s="41"/>
+      <c r="C53" s="41"/>
+      <c r="D53" s="42" t="s">
+        <v>134</v>
+      </c>
+      <c r="E53" s="15"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="43"/>
+      <c r="B54" s="18"/>
+      <c r="C54" s="18"/>
+      <c r="D54" s="44" t="s">
+        <v>135</v>
+      </c>
+      <c r="E54" s="19"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="49">
+        <v>17</v>
+      </c>
+      <c r="B55" s="50" t="s">
+        <v>131</v>
+      </c>
+      <c r="C55" s="50" t="s">
+        <v>73</v>
+      </c>
+      <c r="D55" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="E55" s="52">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="39">
+        <v>18</v>
+      </c>
+      <c r="B56" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D56" s="40" t="s">
+        <v>130</v>
+      </c>
+      <c r="E56" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="14"/>
+      <c r="B57" s="41"/>
+      <c r="C57" s="41"/>
+      <c r="D57" s="42" t="s">
+        <v>134</v>
+      </c>
+      <c r="E57" s="15"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="43"/>
+      <c r="B58" s="18"/>
+      <c r="C58" s="18"/>
+      <c r="D58" s="44" t="s">
+        <v>136</v>
+      </c>
+      <c r="E58" s="19"/>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="35">
+        <v>19</v>
+      </c>
+      <c r="B59" s="36" t="s">
+        <v>131</v>
+      </c>
+      <c r="C59" s="36" t="s">
+        <v>74</v>
+      </c>
+      <c r="D59" s="37" t="s">
+        <v>137</v>
+      </c>
+      <c r="E59" s="38">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="35">
+        <v>20</v>
+      </c>
+      <c r="B60" s="36" t="s">
+        <v>131</v>
+      </c>
+      <c r="C60" s="36" t="s">
+        <v>76</v>
+      </c>
+      <c r="D60" s="37" t="s">
+        <v>138</v>
+      </c>
+      <c r="E60" s="38">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
 </file>
--- a/VPD PO download generator/trying stuff business systems.xlsx
+++ b/VPD PO download generator/trying stuff business systems.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwa25\source\repos\VPD PO download generator\VPD PO download generator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D4E2C95-C771-4C9A-8CE7-0FC2421EDA7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F64DD68B-9A2A-416B-9829-5C44E5247874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{D51960FC-1269-4ACE-8C84-C0CBF6215B21}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{D51960FC-1269-4ACE-8C84-C0CBF6215B21}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -740,7 +740,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -776,18 +776,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
@@ -796,10 +784,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -818,6 +802,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1535,24 +1531,24 @@
       <c r="R4" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="S4" s="31" t="s">
+      <c r="S4" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="T4" s="31"/>
-      <c r="U4" s="31"/>
-      <c r="V4" s="31"/>
+      <c r="T4" s="47"/>
+      <c r="U4" s="47"/>
+      <c r="V4" s="47"/>
       <c r="W4" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Z4" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="AA4" s="32" t="s">
+      <c r="AA4" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="AB4" s="32"/>
-      <c r="AC4" s="32"/>
-      <c r="AD4" s="32"/>
+      <c r="AB4" s="48"/>
+      <c r="AC4" s="48"/>
+      <c r="AD4" s="48"/>
       <c r="AE4" s="7" t="s">
         <v>28</v>
       </c>
@@ -1560,12 +1556,12 @@
       <c r="AH4" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="AI4" s="31" t="s">
+      <c r="AI4" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="AJ4" s="31"/>
-      <c r="AK4" s="31"/>
-      <c r="AL4" s="31"/>
+      <c r="AJ4" s="47"/>
+      <c r="AK4" s="47"/>
+      <c r="AL4" s="47"/>
       <c r="AM4" s="2" t="s">
         <v>29</v>
       </c>
@@ -1899,24 +1895,24 @@
       <c r="R9" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="S9" s="31" t="s">
+      <c r="S9" s="47" t="s">
         <v>62</v>
       </c>
-      <c r="T9" s="31"/>
-      <c r="U9" s="31"/>
-      <c r="V9" s="31"/>
+      <c r="T9" s="47"/>
+      <c r="U9" s="47"/>
+      <c r="V9" s="47"/>
       <c r="W9" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Z9" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="AA9" s="32" t="s">
+      <c r="AA9" s="48" t="s">
         <v>68</v>
       </c>
-      <c r="AB9" s="32"/>
-      <c r="AC9" s="32"/>
-      <c r="AD9" s="32"/>
+      <c r="AB9" s="48"/>
+      <c r="AC9" s="48"/>
+      <c r="AD9" s="48"/>
       <c r="AE9" s="7" t="s">
         <v>28</v>
       </c>
@@ -1924,12 +1920,12 @@
       <c r="AH9" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AI9" s="31" t="s">
+      <c r="AI9" s="47" t="s">
         <v>62</v>
       </c>
-      <c r="AJ9" s="31"/>
-      <c r="AK9" s="31"/>
-      <c r="AL9" s="31"/>
+      <c r="AJ9" s="47"/>
+      <c r="AK9" s="47"/>
+      <c r="AL9" s="47"/>
       <c r="AM9" s="2" t="s">
         <v>29</v>
       </c>
@@ -2219,24 +2215,24 @@
       <c r="R13" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="S13" s="31" t="s">
+      <c r="S13" s="47" t="s">
         <v>64</v>
       </c>
-      <c r="T13" s="31"/>
-      <c r="U13" s="31"/>
-      <c r="V13" s="31"/>
+      <c r="T13" s="47"/>
+      <c r="U13" s="47"/>
+      <c r="V13" s="47"/>
       <c r="W13" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Z13" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="AA13" s="32" t="s">
+      <c r="AA13" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="AB13" s="32"/>
-      <c r="AC13" s="32"/>
-      <c r="AD13" s="32"/>
+      <c r="AB13" s="48"/>
+      <c r="AC13" s="48"/>
+      <c r="AD13" s="48"/>
       <c r="AE13" s="7" t="s">
         <v>28</v>
       </c>
@@ -2397,12 +2393,12 @@
       <c r="AH15" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AI15" s="31" t="s">
+      <c r="AI15" s="47" t="s">
         <v>64</v>
       </c>
-      <c r="AJ15" s="31"/>
-      <c r="AK15" s="31"/>
-      <c r="AL15" s="31"/>
+      <c r="AJ15" s="47"/>
+      <c r="AK15" s="47"/>
+      <c r="AL15" s="47"/>
       <c r="AM15" s="2" t="s">
         <v>29</v>
       </c>
@@ -2563,24 +2559,24 @@
       <c r="R18" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="S18" s="31" t="s">
+      <c r="S18" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="T18" s="31"/>
-      <c r="U18" s="31"/>
-      <c r="V18" s="31"/>
+      <c r="T18" s="47"/>
+      <c r="U18" s="47"/>
+      <c r="V18" s="47"/>
       <c r="W18" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Z18" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="AA18" s="32" t="s">
+      <c r="AA18" s="48" t="s">
         <v>70</v>
       </c>
-      <c r="AB18" s="32"/>
-      <c r="AC18" s="32"/>
-      <c r="AD18" s="32"/>
+      <c r="AB18" s="48"/>
+      <c r="AC18" s="48"/>
+      <c r="AD18" s="48"/>
       <c r="AE18" s="7" t="s">
         <v>28</v>
       </c>
@@ -2805,12 +2801,12 @@
       <c r="AH21" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="AI21" s="31" t="s">
+      <c r="AI21" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="AJ21" s="31"/>
-      <c r="AK21" s="31"/>
-      <c r="AL21" s="31"/>
+      <c r="AJ21" s="47"/>
+      <c r="AK21" s="47"/>
+      <c r="AL21" s="47"/>
       <c r="AM21" s="2" t="s">
         <v>29</v>
       </c>
@@ -2907,12 +2903,12 @@
       <c r="Z23" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AA23" s="31" t="s">
+      <c r="AA23" s="47" t="s">
         <v>75</v>
       </c>
-      <c r="AB23" s="31"/>
-      <c r="AC23" s="31"/>
-      <c r="AD23" s="31"/>
+      <c r="AB23" s="47"/>
+      <c r="AC23" s="47"/>
+      <c r="AD23" s="47"/>
       <c r="AE23" s="2" t="s">
         <v>28</v>
       </c>
@@ -3150,12 +3146,12 @@
       <c r="Z27" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="AA27" s="31" t="s">
+      <c r="AA27" s="47" t="s">
         <v>77</v>
       </c>
-      <c r="AB27" s="31"/>
-      <c r="AC27" s="31"/>
-      <c r="AD27" s="31"/>
+      <c r="AB27" s="47"/>
+      <c r="AC27" s="47"/>
+      <c r="AD27" s="47"/>
       <c r="AE27" s="2" t="s">
         <v>28</v>
       </c>
@@ -4302,6 +4298,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="AA23:AD23"/>
+    <mergeCell ref="AA27:AD27"/>
+    <mergeCell ref="AA4:AD4"/>
+    <mergeCell ref="AA9:AD9"/>
+    <mergeCell ref="AA13:AD13"/>
+    <mergeCell ref="AA18:AD18"/>
     <mergeCell ref="S4:V4"/>
     <mergeCell ref="S9:V9"/>
     <mergeCell ref="S13:V13"/>
@@ -4310,12 +4312,6 @@
     <mergeCell ref="AI4:AL4"/>
     <mergeCell ref="AI9:AL9"/>
     <mergeCell ref="AI15:AL15"/>
-    <mergeCell ref="AA23:AD23"/>
-    <mergeCell ref="AA27:AD27"/>
-    <mergeCell ref="AA4:AD4"/>
-    <mergeCell ref="AA9:AD9"/>
-    <mergeCell ref="AA13:AD13"/>
-    <mergeCell ref="AA18:AD18"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4404,12 +4400,12 @@
       <c r="R2" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="S2" s="31" t="s">
+      <c r="S2" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="T2" s="31"/>
-      <c r="U2" s="31"/>
-      <c r="V2" s="31"/>
+      <c r="T2" s="47"/>
+      <c r="U2" s="47"/>
+      <c r="V2" s="47"/>
       <c r="W2" s="2" t="s">
         <v>26</v>
       </c>
@@ -4569,12 +4565,12 @@
       <c r="Z4" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="AA4" s="32" t="s">
+      <c r="AA4" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="AB4" s="32"/>
-      <c r="AC4" s="32"/>
-      <c r="AD4" s="32"/>
+      <c r="AB4" s="48"/>
+      <c r="AC4" s="48"/>
+      <c r="AD4" s="48"/>
       <c r="AE4" s="7" t="s">
         <v>28</v>
       </c>
@@ -4623,11 +4619,11 @@
       <c r="P5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="V5" s="31" t="s">
+      <c r="V5" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="W5" s="31"/>
-      <c r="X5" s="31"/>
+      <c r="W5" s="47"/>
+      <c r="X5" s="47"/>
       <c r="Y5">
         <v>49</v>
       </c>
@@ -4648,18 +4644,18 @@
       <c r="AI5" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AJ5" s="34" t="s">
+      <c r="AJ5" s="49" t="s">
         <v>80</v>
       </c>
-      <c r="AK5" s="34"/>
+      <c r="AK5" s="49"/>
       <c r="AL5" s="12" t="s">
         <v>81</v>
       </c>
       <c r="AM5" s="12"/>
-      <c r="AN5" s="34" t="s">
+      <c r="AN5" s="49" t="s">
         <v>82</v>
       </c>
-      <c r="AO5" s="34"/>
+      <c r="AO5" s="49"/>
       <c r="AP5" s="12" t="s">
         <v>83</v>
       </c>
@@ -4780,17 +4776,17 @@
       <c r="AI7" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="AJ7" s="31" t="s">
+      <c r="AJ7" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="AK7" s="31"/>
+      <c r="AK7" s="47"/>
       <c r="AL7">
         <v>1</v>
       </c>
-      <c r="AN7" s="31" t="s">
+      <c r="AN7" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="AO7" s="31"/>
+      <c r="AO7" s="47"/>
       <c r="AP7">
         <v>49</v>
       </c>
@@ -4834,12 +4830,12 @@
       <c r="R8" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="S8" s="31" t="s">
+      <c r="S8" s="47" t="s">
         <v>62</v>
       </c>
-      <c r="T8" s="31"/>
-      <c r="U8" s="31"/>
-      <c r="V8" s="31"/>
+      <c r="T8" s="47"/>
+      <c r="U8" s="47"/>
+      <c r="V8" s="47"/>
       <c r="W8" s="2" t="s">
         <v>26</v>
       </c>
@@ -4847,18 +4843,18 @@
       <c r="AI8" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="AJ8" s="33" t="s">
+      <c r="AJ8" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="AK8" s="33"/>
+      <c r="AK8" s="50"/>
       <c r="AL8" s="18">
         <v>1</v>
       </c>
       <c r="AM8" s="18"/>
-      <c r="AN8" s="33" t="s">
+      <c r="AN8" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="AO8" s="33"/>
+      <c r="AO8" s="50"/>
       <c r="AP8" s="18">
         <v>49</v>
       </c>
@@ -4937,12 +4933,12 @@
       <c r="Z9" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="AA9" s="32" t="s">
+      <c r="AA9" s="48" t="s">
         <v>68</v>
       </c>
-      <c r="AB9" s="32"/>
-      <c r="AC9" s="32"/>
-      <c r="AD9" s="32"/>
+      <c r="AB9" s="48"/>
+      <c r="AC9" s="48"/>
+      <c r="AD9" s="48"/>
       <c r="AE9" s="7" t="s">
         <v>28</v>
       </c>
@@ -5071,11 +5067,11 @@
       <c r="P11" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="V11" s="31" t="s">
+      <c r="V11" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="W11" s="31"/>
-      <c r="X11" s="31"/>
+      <c r="W11" s="47"/>
+      <c r="X11" s="47"/>
       <c r="Y11">
         <v>49</v>
       </c>
@@ -5095,18 +5091,18 @@
       <c r="AI11" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AJ11" s="34" t="s">
+      <c r="AJ11" s="49" t="s">
         <v>80</v>
       </c>
-      <c r="AK11" s="34"/>
+      <c r="AK11" s="49"/>
       <c r="AL11" s="12" t="s">
         <v>81</v>
       </c>
       <c r="AM11" s="12"/>
-      <c r="AN11" s="34" t="s">
+      <c r="AN11" s="49" t="s">
         <v>82</v>
       </c>
-      <c r="AO11" s="34"/>
+      <c r="AO11" s="49"/>
       <c r="AP11" s="12" t="s">
         <v>83</v>
       </c>
@@ -5198,12 +5194,12 @@
       <c r="Z13" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="AA13" s="32" t="s">
+      <c r="AA13" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="AB13" s="32"/>
-      <c r="AC13" s="32"/>
-      <c r="AD13" s="32"/>
+      <c r="AB13" s="48"/>
+      <c r="AC13" s="48"/>
+      <c r="AD13" s="48"/>
       <c r="AE13" s="7" t="s">
         <v>28</v>
       </c>
@@ -5211,18 +5207,18 @@
       <c r="AI13" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="AJ13" s="33" t="s">
+      <c r="AJ13" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="AK13" s="33"/>
+      <c r="AK13" s="50"/>
       <c r="AL13" s="18">
         <v>1</v>
       </c>
       <c r="AM13" s="18"/>
-      <c r="AN13" s="33" t="s">
+      <c r="AN13" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="AO13" s="33"/>
+      <c r="AO13" s="50"/>
       <c r="AP13" s="18">
         <v>49</v>
       </c>
@@ -5282,12 +5278,12 @@
       <c r="R14" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="S14" s="31" t="s">
+      <c r="S14" s="47" t="s">
         <v>64</v>
       </c>
-      <c r="T14" s="31"/>
-      <c r="U14" s="31"/>
-      <c r="V14" s="31"/>
+      <c r="T14" s="47"/>
+      <c r="U14" s="47"/>
+      <c r="V14" s="47"/>
       <c r="W14" s="2" t="s">
         <v>26</v>
       </c>
@@ -5307,10 +5303,10 @@
       <c r="AF14" s="2"/>
       <c r="AG14" s="2"/>
       <c r="AI14" s="2"/>
-      <c r="AJ14" s="31"/>
-      <c r="AK14" s="31"/>
-      <c r="AN14" s="31"/>
-      <c r="AO14" s="31"/>
+      <c r="AJ14" s="47"/>
+      <c r="AK14" s="47"/>
+      <c r="AN14" s="47"/>
+      <c r="AO14" s="47"/>
     </row>
     <row r="15" spans="2:53" x14ac:dyDescent="0.25">
       <c r="B15">
@@ -5456,18 +5452,18 @@
       <c r="AI16" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AJ16" s="34" t="s">
+      <c r="AJ16" s="49" t="s">
         <v>80</v>
       </c>
-      <c r="AK16" s="34"/>
+      <c r="AK16" s="49"/>
       <c r="AL16" s="12" t="s">
         <v>81</v>
       </c>
       <c r="AM16" s="12"/>
-      <c r="AN16" s="34" t="s">
+      <c r="AN16" s="49" t="s">
         <v>82</v>
       </c>
-      <c r="AO16" s="34"/>
+      <c r="AO16" s="49"/>
       <c r="AP16" s="12" t="s">
         <v>83</v>
       </c>
@@ -5522,11 +5518,11 @@
       <c r="P17" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="V17" s="31" t="s">
+      <c r="V17" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="W17" s="31"/>
-      <c r="X17" s="31"/>
+      <c r="W17" s="47"/>
+      <c r="X17" s="47"/>
       <c r="Y17">
         <v>49</v>
       </c>
@@ -5567,12 +5563,12 @@
       <c r="Z18" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="AA18" s="32" t="s">
+      <c r="AA18" s="48" t="s">
         <v>70</v>
       </c>
-      <c r="AB18" s="32"/>
-      <c r="AC18" s="32"/>
-      <c r="AD18" s="32"/>
+      <c r="AB18" s="48"/>
+      <c r="AC18" s="48"/>
+      <c r="AD18" s="48"/>
       <c r="AE18" s="7" t="s">
         <v>28</v>
       </c>
@@ -5580,18 +5576,18 @@
       <c r="AI18" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="AJ18" s="33" t="s">
+      <c r="AJ18" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="AK18" s="33"/>
+      <c r="AK18" s="50"/>
       <c r="AL18" s="18">
         <v>1</v>
       </c>
       <c r="AM18" s="18"/>
-      <c r="AN18" s="33" t="s">
+      <c r="AN18" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="AO18" s="33"/>
+      <c r="AO18" s="50"/>
       <c r="AP18" s="18">
         <v>49</v>
       </c>
@@ -5709,12 +5705,12 @@
       <c r="R20" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="S20" s="31" t="s">
+      <c r="S20" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="T20" s="31"/>
-      <c r="U20" s="31"/>
-      <c r="V20" s="31"/>
+      <c r="T20" s="47"/>
+      <c r="U20" s="47"/>
+      <c r="V20" s="47"/>
       <c r="W20" s="2" t="s">
         <v>26</v>
       </c>
@@ -5735,18 +5731,18 @@
       <c r="AI20" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AJ20" s="34" t="s">
+      <c r="AJ20" s="49" t="s">
         <v>80</v>
       </c>
-      <c r="AK20" s="34"/>
+      <c r="AK20" s="49"/>
       <c r="AL20" s="12" t="s">
         <v>81</v>
       </c>
       <c r="AM20" s="12"/>
-      <c r="AN20" s="34" t="s">
+      <c r="AN20" s="49" t="s">
         <v>82</v>
       </c>
-      <c r="AO20" s="34"/>
+      <c r="AO20" s="49"/>
       <c r="AP20" s="12" t="s">
         <v>83</v>
       </c>
@@ -5895,18 +5891,18 @@
       <c r="AI22" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="AJ22" s="33" t="s">
+      <c r="AJ22" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="AK22" s="33"/>
+      <c r="AK22" s="50"/>
       <c r="AL22" s="18">
         <v>2</v>
       </c>
       <c r="AM22" s="18"/>
-      <c r="AN22" s="33" t="s">
+      <c r="AN22" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="AO22" s="33"/>
+      <c r="AO22" s="50"/>
       <c r="AP22" s="18">
         <v>2</v>
       </c>
@@ -5947,11 +5943,11 @@
       <c r="I23">
         <v>21</v>
       </c>
-      <c r="V23" s="31" t="s">
+      <c r="V23" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="W23" s="31"/>
-      <c r="X23" s="31"/>
+      <c r="W23" s="47"/>
+      <c r="X23" s="47"/>
       <c r="Y23">
         <v>49</v>
       </c>
@@ -6002,18 +5998,18 @@
       <c r="AI24" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AJ24" s="34" t="s">
+      <c r="AJ24" s="49" t="s">
         <v>80</v>
       </c>
-      <c r="AK24" s="34"/>
+      <c r="AK24" s="49"/>
       <c r="AL24" s="12" t="s">
         <v>81</v>
       </c>
       <c r="AM24" s="12"/>
-      <c r="AN24" s="34" t="s">
+      <c r="AN24" s="49" t="s">
         <v>82</v>
       </c>
-      <c r="AO24" s="34"/>
+      <c r="AO24" s="49"/>
       <c r="AP24" s="12" t="s">
         <v>83</v>
       </c>
@@ -6098,12 +6094,12 @@
       <c r="R26" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="S26" s="31" t="s">
+      <c r="S26" s="47" t="s">
         <v>75</v>
       </c>
-      <c r="T26" s="31"/>
-      <c r="U26" s="31"/>
-      <c r="V26" s="31"/>
+      <c r="T26" s="47"/>
+      <c r="U26" s="47"/>
+      <c r="V26" s="47"/>
       <c r="W26" s="2" t="s">
         <v>28</v>
       </c>
@@ -6111,18 +6107,18 @@
       <c r="AI26" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="AJ26" s="33" t="s">
+      <c r="AJ26" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="AK26" s="33"/>
+      <c r="AK26" s="50"/>
       <c r="AL26" s="18">
         <v>2</v>
       </c>
       <c r="AM26" s="18"/>
-      <c r="AN26" s="33" t="s">
+      <c r="AN26" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="AO26" s="33"/>
+      <c r="AO26" s="50"/>
       <c r="AP26" s="18">
         <v>2</v>
       </c>
@@ -6292,29 +6288,29 @@
       <c r="P29" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="V29" s="31" t="s">
+      <c r="V29" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="W29" s="31"/>
-      <c r="X29" s="31"/>
+      <c r="W29" s="47"/>
+      <c r="X29" s="47"/>
       <c r="Y29" s="10">
         <v>2</v>
       </c>
       <c r="AI29" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AJ29" s="34" t="s">
+      <c r="AJ29" s="49" t="s">
         <v>80</v>
       </c>
-      <c r="AK29" s="34"/>
+      <c r="AK29" s="49"/>
       <c r="AL29" s="12" t="s">
         <v>81</v>
       </c>
       <c r="AM29" s="12"/>
-      <c r="AN29" s="34" t="s">
+      <c r="AN29" s="49" t="s">
         <v>82</v>
       </c>
-      <c r="AO29" s="34"/>
+      <c r="AO29" s="49"/>
       <c r="AP29" s="12" t="s">
         <v>83</v>
       </c>
@@ -6422,17 +6418,17 @@
       <c r="AI31" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="AJ31" s="31" t="s">
+      <c r="AJ31" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="AK31" s="31"/>
+      <c r="AK31" s="47"/>
       <c r="AL31">
         <v>3</v>
       </c>
-      <c r="AN31" s="31" t="s">
+      <c r="AN31" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="AO31" s="31"/>
+      <c r="AO31" s="47"/>
       <c r="AP31">
         <v>4</v>
       </c>
@@ -6492,12 +6488,12 @@
       <c r="R32" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="S32" s="31" t="s">
+      <c r="S32" s="47" t="s">
         <v>77</v>
       </c>
-      <c r="T32" s="31"/>
-      <c r="U32" s="31"/>
-      <c r="V32" s="31"/>
+      <c r="T32" s="47"/>
+      <c r="U32" s="47"/>
+      <c r="V32" s="47"/>
       <c r="W32" s="2" t="s">
         <v>28</v>
       </c>
@@ -6505,17 +6501,17 @@
       <c r="AI32" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="AJ32" s="31" t="s">
+      <c r="AJ32" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="AK32" s="31"/>
+      <c r="AK32" s="47"/>
       <c r="AL32">
         <v>3</v>
       </c>
-      <c r="AN32" s="31" t="s">
+      <c r="AN32" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="AO32" s="31"/>
+      <c r="AO32" s="47"/>
       <c r="AP32">
         <v>4</v>
       </c>
@@ -6578,17 +6574,17 @@
       <c r="AI33" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="AJ33" s="31" t="s">
+      <c r="AJ33" s="47" t="s">
         <v>40</v>
       </c>
-      <c r="AK33" s="31"/>
+      <c r="AK33" s="47"/>
       <c r="AL33">
         <v>5</v>
       </c>
-      <c r="AN33" s="31" t="s">
+      <c r="AN33" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="AO33" s="31"/>
+      <c r="AO33" s="47"/>
       <c r="AP33">
         <v>6</v>
       </c>
@@ -6670,18 +6666,18 @@
       <c r="AI34" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="AJ34" s="33" t="s">
+      <c r="AJ34" s="50" t="s">
         <v>40</v>
       </c>
-      <c r="AK34" s="33"/>
+      <c r="AK34" s="50"/>
       <c r="AL34" s="18">
         <v>5</v>
       </c>
       <c r="AM34" s="18"/>
-      <c r="AN34" s="33" t="s">
+      <c r="AN34" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="AO34" s="33"/>
+      <c r="AO34" s="50"/>
       <c r="AP34" s="18">
         <v>6</v>
       </c>
@@ -6738,11 +6734,11 @@
       <c r="P35" t="s">
         <v>29</v>
       </c>
-      <c r="V35" s="31" t="s">
+      <c r="V35" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="W35" s="31"/>
-      <c r="X35" s="31"/>
+      <c r="W35" s="47"/>
+      <c r="X35" s="47"/>
       <c r="Y35" s="10">
         <v>2</v>
       </c>
@@ -6811,18 +6807,18 @@
       <c r="AI37" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AJ37" s="34" t="s">
+      <c r="AJ37" s="49" t="s">
         <v>80</v>
       </c>
-      <c r="AK37" s="34"/>
+      <c r="AK37" s="49"/>
       <c r="AL37" s="12" t="s">
         <v>81</v>
       </c>
       <c r="AM37" s="12"/>
-      <c r="AN37" s="34" t="s">
+      <c r="AN37" s="49" t="s">
         <v>82</v>
       </c>
-      <c r="AO37" s="34"/>
+      <c r="AO37" s="49"/>
       <c r="AP37" s="12" t="s">
         <v>83</v>
       </c>
@@ -6838,12 +6834,12 @@
       <c r="R38" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="S38" s="31" t="s">
+      <c r="S38" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="T38" s="31"/>
-      <c r="U38" s="31"/>
-      <c r="V38" s="31"/>
+      <c r="T38" s="47"/>
+      <c r="U38" s="47"/>
+      <c r="V38" s="47"/>
       <c r="W38" s="2" t="s">
         <v>29</v>
       </c>
@@ -6894,18 +6890,18 @@
       <c r="AI39" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="AJ39" s="33" t="s">
+      <c r="AJ39" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="AK39" s="33"/>
+      <c r="AK39" s="50"/>
       <c r="AL39" s="18">
         <v>3</v>
       </c>
       <c r="AM39" s="18"/>
-      <c r="AN39" s="33" t="s">
+      <c r="AN39" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="AO39" s="33"/>
+      <c r="AO39" s="50"/>
       <c r="AP39" s="18">
         <v>4</v>
       </c>
@@ -7016,29 +7012,29 @@
       <c r="P42" t="s">
         <v>43</v>
       </c>
-      <c r="V42" s="31" t="s">
+      <c r="V42" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="W42" s="31"/>
-      <c r="X42" s="31"/>
+      <c r="W42" s="47"/>
+      <c r="X42" s="47"/>
       <c r="Y42">
         <v>6</v>
       </c>
       <c r="AI42" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AJ42" s="34" t="s">
+      <c r="AJ42" s="49" t="s">
         <v>80</v>
       </c>
-      <c r="AK42" s="34"/>
+      <c r="AK42" s="49"/>
       <c r="AL42" s="12" t="s">
         <v>81</v>
       </c>
       <c r="AM42" s="12"/>
-      <c r="AN42" s="34" t="s">
+      <c r="AN42" s="49" t="s">
         <v>82</v>
       </c>
-      <c r="AO42" s="34"/>
+      <c r="AO42" s="49"/>
       <c r="AP42" s="12" t="s">
         <v>83</v>
       </c>
@@ -7078,18 +7074,18 @@
       <c r="AI44" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="AJ44" s="33" t="s">
+      <c r="AJ44" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="AK44" s="33"/>
+      <c r="AK44" s="50"/>
       <c r="AL44" s="18">
         <v>3</v>
       </c>
       <c r="AM44" s="18"/>
-      <c r="AN44" s="33" t="s">
+      <c r="AN44" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="AO44" s="33"/>
+      <c r="AO44" s="50"/>
       <c r="AP44" s="18">
         <v>4</v>
       </c>
@@ -7123,12 +7119,12 @@
       <c r="R45" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="S45" s="31" t="s">
+      <c r="S45" s="47" t="s">
         <v>62</v>
       </c>
-      <c r="T45" s="31"/>
-      <c r="U45" s="31"/>
-      <c r="V45" s="31"/>
+      <c r="T45" s="47"/>
+      <c r="U45" s="47"/>
+      <c r="V45" s="47"/>
       <c r="W45" s="2" t="s">
         <v>29</v>
       </c>
@@ -7173,18 +7169,18 @@
       <c r="AI46" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AJ46" s="34" t="s">
+      <c r="AJ46" s="49" t="s">
         <v>80</v>
       </c>
-      <c r="AK46" s="34"/>
+      <c r="AK46" s="49"/>
       <c r="AL46" s="12" t="s">
         <v>81</v>
       </c>
       <c r="AM46" s="12"/>
-      <c r="AN46" s="34" t="s">
+      <c r="AN46" s="49" t="s">
         <v>82</v>
       </c>
-      <c r="AO46" s="34"/>
+      <c r="AO46" s="49"/>
       <c r="AP46" s="12" t="s">
         <v>83</v>
       </c>
@@ -7268,18 +7264,18 @@
       <c r="AI48" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="AJ48" s="33" t="s">
+      <c r="AJ48" s="50" t="s">
         <v>40</v>
       </c>
-      <c r="AK48" s="33"/>
+      <c r="AK48" s="50"/>
       <c r="AL48" s="18">
         <v>5</v>
       </c>
       <c r="AM48" s="18"/>
-      <c r="AN48" s="33" t="s">
+      <c r="AN48" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="AO48" s="33"/>
+      <c r="AO48" s="50"/>
       <c r="AP48" s="18">
         <v>6</v>
       </c>
@@ -7310,11 +7306,11 @@
       <c r="P49" t="s">
         <v>43</v>
       </c>
-      <c r="V49" s="31" t="s">
+      <c r="V49" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="W49" s="31"/>
-      <c r="X49" s="31"/>
+      <c r="W49" s="47"/>
+      <c r="X49" s="47"/>
       <c r="Y49">
         <v>6</v>
       </c>
@@ -7375,12 +7371,12 @@
       <c r="R52" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="S52" s="31" t="s">
+      <c r="S52" s="47" t="s">
         <v>64</v>
       </c>
-      <c r="T52" s="31"/>
-      <c r="U52" s="31"/>
-      <c r="V52" s="31"/>
+      <c r="T52" s="47"/>
+      <c r="U52" s="47"/>
+      <c r="V52" s="47"/>
       <c r="W52" s="2" t="s">
         <v>29</v>
       </c>
@@ -7504,11 +7500,11 @@
       <c r="P56" t="s">
         <v>43</v>
       </c>
-      <c r="V56" s="31" t="s">
+      <c r="V56" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="W56" s="31"/>
-      <c r="X56" s="31"/>
+      <c r="W56" s="47"/>
+      <c r="X56" s="47"/>
       <c r="Y56">
         <v>6</v>
       </c>
@@ -7551,12 +7547,12 @@
       <c r="R59" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="S59" s="31" t="s">
+      <c r="S59" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="T59" s="31"/>
-      <c r="U59" s="31"/>
-      <c r="V59" s="31"/>
+      <c r="T59" s="47"/>
+      <c r="U59" s="47"/>
+      <c r="V59" s="47"/>
       <c r="W59" s="2" t="s">
         <v>29</v>
       </c>
@@ -7679,11 +7675,11 @@
       <c r="Y62" s="10"/>
     </row>
     <row r="63" spans="12:25" x14ac:dyDescent="0.25">
-      <c r="V63" s="31" t="s">
+      <c r="V63" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="W63" s="31"/>
-      <c r="X63" s="31"/>
+      <c r="W63" s="47"/>
+      <c r="X63" s="47"/>
       <c r="Y63">
         <v>4</v>
       </c>
@@ -8050,23 +8046,43 @@
     </row>
   </sheetData>
   <mergeCells count="70">
-    <mergeCell ref="S2:V2"/>
-    <mergeCell ref="AA4:AD4"/>
-    <mergeCell ref="S38:V38"/>
-    <mergeCell ref="S8:V8"/>
-    <mergeCell ref="AA9:AD9"/>
-    <mergeCell ref="V29:X29"/>
-    <mergeCell ref="S14:V14"/>
-    <mergeCell ref="AA13:AD13"/>
-    <mergeCell ref="S20:V20"/>
-    <mergeCell ref="AA18:AD18"/>
-    <mergeCell ref="S59:V59"/>
-    <mergeCell ref="V35:X35"/>
-    <mergeCell ref="V42:X42"/>
-    <mergeCell ref="V49:X49"/>
-    <mergeCell ref="V56:X56"/>
-    <mergeCell ref="S45:V45"/>
-    <mergeCell ref="S52:V52"/>
+    <mergeCell ref="AJ44:AK44"/>
+    <mergeCell ref="AN44:AO44"/>
+    <mergeCell ref="AJ46:AK46"/>
+    <mergeCell ref="AN46:AO46"/>
+    <mergeCell ref="AJ48:AK48"/>
+    <mergeCell ref="AN48:AO48"/>
+    <mergeCell ref="AJ42:AK42"/>
+    <mergeCell ref="AN42:AO42"/>
+    <mergeCell ref="AJ34:AK34"/>
+    <mergeCell ref="AN34:AO34"/>
+    <mergeCell ref="AJ37:AK37"/>
+    <mergeCell ref="AN37:AO37"/>
+    <mergeCell ref="AJ39:AK39"/>
+    <mergeCell ref="AN39:AO39"/>
+    <mergeCell ref="AJ31:AK31"/>
+    <mergeCell ref="AN31:AO31"/>
+    <mergeCell ref="AJ32:AK32"/>
+    <mergeCell ref="AN32:AO32"/>
+    <mergeCell ref="AJ33:AK33"/>
+    <mergeCell ref="AN33:AO33"/>
+    <mergeCell ref="AJ24:AK24"/>
+    <mergeCell ref="AN24:AO24"/>
+    <mergeCell ref="AJ26:AK26"/>
+    <mergeCell ref="AN26:AO26"/>
+    <mergeCell ref="AJ29:AK29"/>
+    <mergeCell ref="AN29:AO29"/>
+    <mergeCell ref="AJ18:AK18"/>
+    <mergeCell ref="AN18:AO18"/>
+    <mergeCell ref="AJ20:AK20"/>
+    <mergeCell ref="AN20:AO20"/>
+    <mergeCell ref="AJ22:AK22"/>
+    <mergeCell ref="AN22:AO22"/>
+    <mergeCell ref="AN13:AO13"/>
+    <mergeCell ref="AJ14:AK14"/>
+    <mergeCell ref="AN14:AO14"/>
+    <mergeCell ref="AJ16:AK16"/>
+    <mergeCell ref="AN16:AO16"/>
     <mergeCell ref="V63:X63"/>
     <mergeCell ref="AJ5:AK5"/>
     <mergeCell ref="AN5:AO5"/>
@@ -8083,43 +8099,23 @@
     <mergeCell ref="V11:X11"/>
     <mergeCell ref="V17:X17"/>
     <mergeCell ref="V23:X23"/>
-    <mergeCell ref="AN13:AO13"/>
-    <mergeCell ref="AJ14:AK14"/>
-    <mergeCell ref="AN14:AO14"/>
-    <mergeCell ref="AJ16:AK16"/>
-    <mergeCell ref="AN16:AO16"/>
-    <mergeCell ref="AJ18:AK18"/>
-    <mergeCell ref="AN18:AO18"/>
-    <mergeCell ref="AJ20:AK20"/>
-    <mergeCell ref="AN20:AO20"/>
-    <mergeCell ref="AJ22:AK22"/>
-    <mergeCell ref="AN22:AO22"/>
-    <mergeCell ref="AJ24:AK24"/>
-    <mergeCell ref="AN24:AO24"/>
-    <mergeCell ref="AJ26:AK26"/>
-    <mergeCell ref="AN26:AO26"/>
-    <mergeCell ref="AJ29:AK29"/>
-    <mergeCell ref="AN29:AO29"/>
-    <mergeCell ref="AJ31:AK31"/>
-    <mergeCell ref="AN31:AO31"/>
-    <mergeCell ref="AJ32:AK32"/>
-    <mergeCell ref="AN32:AO32"/>
-    <mergeCell ref="AJ33:AK33"/>
-    <mergeCell ref="AN33:AO33"/>
-    <mergeCell ref="AJ42:AK42"/>
-    <mergeCell ref="AN42:AO42"/>
-    <mergeCell ref="AJ34:AK34"/>
-    <mergeCell ref="AN34:AO34"/>
-    <mergeCell ref="AJ37:AK37"/>
-    <mergeCell ref="AN37:AO37"/>
-    <mergeCell ref="AJ39:AK39"/>
-    <mergeCell ref="AN39:AO39"/>
-    <mergeCell ref="AJ44:AK44"/>
-    <mergeCell ref="AN44:AO44"/>
-    <mergeCell ref="AJ46:AK46"/>
-    <mergeCell ref="AN46:AO46"/>
-    <mergeCell ref="AJ48:AK48"/>
-    <mergeCell ref="AN48:AO48"/>
+    <mergeCell ref="S59:V59"/>
+    <mergeCell ref="V35:X35"/>
+    <mergeCell ref="V42:X42"/>
+    <mergeCell ref="V49:X49"/>
+    <mergeCell ref="V56:X56"/>
+    <mergeCell ref="S45:V45"/>
+    <mergeCell ref="S52:V52"/>
+    <mergeCell ref="S2:V2"/>
+    <mergeCell ref="AA4:AD4"/>
+    <mergeCell ref="S38:V38"/>
+    <mergeCell ref="S8:V8"/>
+    <mergeCell ref="AA9:AD9"/>
+    <mergeCell ref="V29:X29"/>
+    <mergeCell ref="S14:V14"/>
+    <mergeCell ref="AA13:AD13"/>
+    <mergeCell ref="S20:V20"/>
+    <mergeCell ref="AA18:AD18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9566,7 +9562,7 @@
         <v>132</v>
       </c>
       <c r="E32">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="H32" t="s">
         <v>128</v>
@@ -9729,24 +9725,24 @@
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="45">
+      <c r="A43" s="39">
         <v>11</v>
       </c>
-      <c r="B43" s="46" t="s">
+      <c r="B43" s="40" t="s">
         <v>131</v>
       </c>
-      <c r="C43" s="46" t="s">
+      <c r="C43" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="D43" s="47" t="s">
+      <c r="D43" s="41" t="s">
         <v>133</v>
       </c>
-      <c r="E43" s="48">
+      <c r="E43" s="42">
         <v>-1</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="39">
+      <c r="A44" s="35">
         <v>12</v>
       </c>
       <c r="B44" s="12" t="s">
@@ -9755,7 +9751,7 @@
       <c r="C44" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="D44" s="40" t="s">
+      <c r="D44" s="36" t="s">
         <v>130</v>
       </c>
       <c r="E44" s="13">
@@ -9764,41 +9760,39 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="14"/>
-      <c r="B45" s="41"/>
-      <c r="C45" s="41"/>
-      <c r="D45" s="42" t="s">
+      <c r="D45" s="28" t="s">
         <v>134</v>
       </c>
       <c r="E45" s="15"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="43"/>
+      <c r="A46" s="37"/>
       <c r="B46" s="18"/>
       <c r="C46" s="18"/>
-      <c r="D46" s="44" t="s">
+      <c r="D46" s="38" t="s">
         <v>135</v>
       </c>
       <c r="E46" s="19"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="45">
+      <c r="A47" s="39">
         <v>13</v>
       </c>
-      <c r="B47" s="46" t="s">
+      <c r="B47" s="40" t="s">
         <v>131</v>
       </c>
-      <c r="C47" s="46" t="s">
+      <c r="C47" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="D47" s="47" t="s">
+      <c r="D47" s="41" t="s">
         <v>133</v>
       </c>
-      <c r="E47" s="48">
+      <c r="E47" s="42">
         <v>-1</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="39">
+      <c r="A48" s="35">
         <v>14</v>
       </c>
       <c r="B48" s="12" t="s">
@@ -9807,7 +9801,7 @@
       <c r="C48" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="D48" s="40" t="s">
+      <c r="D48" s="36" t="s">
         <v>130</v>
       </c>
       <c r="E48" s="13">
@@ -9816,41 +9810,39 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="14"/>
-      <c r="B49" s="41"/>
-      <c r="C49" s="41"/>
-      <c r="D49" s="42" t="s">
+      <c r="D49" s="28" t="s">
         <v>134</v>
       </c>
       <c r="E49" s="15"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="43"/>
+      <c r="A50" s="37"/>
       <c r="B50" s="18"/>
       <c r="C50" s="18"/>
-      <c r="D50" s="44" t="s">
+      <c r="D50" s="38" t="s">
         <v>136</v>
       </c>
       <c r="E50" s="19"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="45">
+      <c r="A51" s="39">
         <v>15</v>
       </c>
-      <c r="B51" s="46" t="s">
+      <c r="B51" s="40" t="s">
         <v>131</v>
       </c>
-      <c r="C51" s="46" t="s">
+      <c r="C51" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="D51" s="47" t="s">
+      <c r="D51" s="41" t="s">
         <v>133</v>
       </c>
-      <c r="E51" s="48">
+      <c r="E51" s="42">
         <v>-1</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="39">
+      <c r="A52" s="35">
         <v>16</v>
       </c>
       <c r="B52" s="12" t="s">
@@ -9859,7 +9851,7 @@
       <c r="C52" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="D52" s="40" t="s">
+      <c r="D52" s="36" t="s">
         <v>130</v>
       </c>
       <c r="E52" s="13">
@@ -9868,41 +9860,39 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="14"/>
-      <c r="B53" s="41"/>
-      <c r="C53" s="41"/>
-      <c r="D53" s="42" t="s">
+      <c r="D53" s="28" t="s">
         <v>134</v>
       </c>
       <c r="E53" s="15"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="43"/>
+      <c r="A54" s="37"/>
       <c r="B54" s="18"/>
       <c r="C54" s="18"/>
-      <c r="D54" s="44" t="s">
+      <c r="D54" s="38" t="s">
         <v>135</v>
       </c>
       <c r="E54" s="19"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="49">
+      <c r="A55" s="43">
         <v>17</v>
       </c>
-      <c r="B55" s="50" t="s">
+      <c r="B55" s="44" t="s">
         <v>131</v>
       </c>
-      <c r="C55" s="50" t="s">
+      <c r="C55" s="44" t="s">
         <v>73</v>
       </c>
-      <c r="D55" s="51" t="s">
+      <c r="D55" s="45" t="s">
         <v>133</v>
       </c>
-      <c r="E55" s="52">
+      <c r="E55" s="46">
         <v>-1</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="39">
+      <c r="A56" s="35">
         <v>18</v>
       </c>
       <c r="B56" s="12" t="s">
@@ -9911,7 +9901,7 @@
       <c r="C56" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="D56" s="40" t="s">
+      <c r="D56" s="36" t="s">
         <v>130</v>
       </c>
       <c r="E56" s="13">
@@ -9920,53 +9910,51 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="14"/>
-      <c r="B57" s="41"/>
-      <c r="C57" s="41"/>
-      <c r="D57" s="42" t="s">
+      <c r="D57" s="28" t="s">
         <v>134</v>
       </c>
       <c r="E57" s="15"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="43"/>
+      <c r="A58" s="37"/>
       <c r="B58" s="18"/>
       <c r="C58" s="18"/>
-      <c r="D58" s="44" t="s">
+      <c r="D58" s="38" t="s">
         <v>136</v>
       </c>
       <c r="E58" s="19"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="35">
+      <c r="A59" s="31">
         <v>19</v>
       </c>
-      <c r="B59" s="36" t="s">
+      <c r="B59" s="32" t="s">
         <v>131</v>
       </c>
-      <c r="C59" s="36" t="s">
+      <c r="C59" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="D59" s="37" t="s">
+      <c r="D59" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="E59" s="38">
+      <c r="E59" s="34">
         <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="35">
+      <c r="A60" s="31">
         <v>20</v>
       </c>
-      <c r="B60" s="36" t="s">
+      <c r="B60" s="32" t="s">
         <v>131</v>
       </c>
-      <c r="C60" s="36" t="s">
+      <c r="C60" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="D60" s="37" t="s">
+      <c r="D60" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="E60" s="38">
+      <c r="E60" s="34">
         <v>7</v>
       </c>
     </row>

--- a/VPD PO download generator/trying stuff business systems.xlsx
+++ b/VPD PO download generator/trying stuff business systems.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwa25\source\repos\VPD PO download generator\VPD PO download generator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F64DD68B-9A2A-416B-9829-5C44E5247874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9750C3A5-C3C5-4EB7-9227-5D2875E77025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{D51960FC-1269-4ACE-8C84-C0CBF6215B21}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{D51960FC-1269-4ACE-8C84-C0CBF6215B21}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1397" uniqueCount="148">
   <si>
     <t>KSO5088990 PVPDFJB    TWHWHNA01AA001CR-SO-5088990-1-1                                            L07975</t>
   </si>
@@ -447,6 +447,33 @@
   </si>
   <si>
     <t>7,7</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> profileID: str</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> length: float</t>
+  </si>
+  <si>
+    <t>Handing</t>
+  </si>
+  <si>
+    <t>frameWelderQRCode</t>
+  </si>
+  <si>
+    <t>panelWelderQRCode</t>
+  </si>
+  <si>
+    <t>cartID</t>
+  </si>
+  <si>
+    <t>cartBin</t>
+  </si>
+  <si>
+    <t>panelComponentsNeeded</t>
+  </si>
+  <si>
+    <t>panelComponentsCut</t>
   </si>
 </sst>
 </file>
@@ -740,7 +767,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -813,6 +840,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8123,44 +8157,44 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D31D181-2758-43CB-B29A-A87F826596E0}">
-  <dimension ref="A3:Q52"/>
+  <dimension ref="A3:U52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.140625" customWidth="1"/>
     <col min="2" max="2" width="28.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.5703125" customWidth="1"/>
     <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
     <col min="9" max="9" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23" customWidth="1"/>
-    <col min="14" max="14" width="1.5703125" customWidth="1"/>
-    <col min="15" max="15" width="18.140625" customWidth="1"/>
-    <col min="16" max="16" width="1.42578125" customWidth="1"/>
-    <col min="17" max="17" width="45.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="23" customWidth="1"/>
+    <col min="18" max="18" width="1.5703125" customWidth="1"/>
+    <col min="19" max="19" width="18.140625" customWidth="1"/>
+    <col min="20" max="20" width="1.42578125" customWidth="1"/>
+    <col min="21" max="21" width="45.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>104</v>
       </c>
-      <c r="M7" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="O7" s="23" t="s">
-        <v>107</v>
-      </c>
       <c r="Q7" s="23" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="S7" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="U7" s="23" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="63" x14ac:dyDescent="0.25">
       <c r="B8" s="20" t="s">
         <v>91</v>
       </c>
@@ -8185,17 +8219,38 @@
       <c r="I8" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="M8" s="26" t="s">
+      <c r="J8" s="51" t="s">
+        <v>141</v>
+      </c>
+      <c r="K8" s="51" t="s">
+        <v>144</v>
+      </c>
+      <c r="L8" t="s">
+        <v>145</v>
+      </c>
+      <c r="M8" s="52" t="s">
+        <v>142</v>
+      </c>
+      <c r="N8" s="52" t="s">
+        <v>143</v>
+      </c>
+      <c r="O8" s="52" t="s">
+        <v>146</v>
+      </c>
+      <c r="P8" s="53" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q8" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="O8" s="26" t="s">
+      <c r="S8" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="Q8" s="26" t="s">
+      <c r="U8" s="26" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>98</v>
       </c>
@@ -8220,17 +8275,17 @@
       <c r="I9" t="s">
         <v>102</v>
       </c>
-      <c r="M9" s="24" t="s">
+      <c r="Q9" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="O9" s="24" t="s">
+      <c r="S9" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="Q9" s="24" t="s">
+      <c r="U9" s="24" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>103</v>
       </c>
@@ -8255,38 +8310,44 @@
       <c r="I10" t="s">
         <v>102</v>
       </c>
-      <c r="M10" s="24" t="s">
+      <c r="Q10" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="O10" s="25" t="s">
+      <c r="S10" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="Q10" s="24" t="s">
+      <c r="U10" s="24" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M11" s="24" t="s">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="Q11" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="Q11" s="24" t="s">
+      <c r="U11" s="24" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M12" s="24" t="s">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="Q12" s="24" t="s">
         <v>112</v>
       </c>
-      <c r="Q12" s="25" t="s">
+      <c r="S12" t="s">
+        <v>139</v>
+      </c>
+      <c r="U12" s="25" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="M13" s="25" t="s">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="Q13" s="25" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>105</v>
       </c>
